--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-24).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-24).xlsx
@@ -935,94 +935,94 @@
     <t>214</t>
   </si>
   <si>
-    <t>83</t>
-  </si>
-  <si>
-    <t>R$ 4.719,98</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>33.7</t>
-  </si>
-  <si>
-    <t>4.80</t>
-  </si>
-  <si>
-    <t>18.2</t>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 4.650,01</t>
+  </si>
+  <si>
+    <t>51.2</t>
+  </si>
+  <si>
+    <t>32.3</t>
+  </si>
+  <si>
+    <t>4.96</t>
+  </si>
+  <si>
+    <t>18.6</t>
   </si>
   <si>
     <t>6.9</t>
   </si>
   <si>
-    <t>4.2</t>
-  </si>
-  <si>
-    <t>46.4%</t>
-  </si>
-  <si>
-    <t>18.2%</t>
-  </si>
-  <si>
-    <t>1.5%</t>
+    <t>6.1</t>
+  </si>
+  <si>
+    <t>43.5%</t>
+  </si>
+  <si>
+    <t>19.0%</t>
+  </si>
+  <si>
+    <t>1.6%</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>5.9%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>7.0%</t>
-  </si>
-  <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>946.0</t>
-  </si>
-  <si>
-    <t>760.0</t>
-  </si>
-  <si>
-    <t>63.0</t>
-  </si>
-  <si>
-    <t>17.0</t>
-  </si>
-  <si>
-    <t>246.0</t>
-  </si>
-  <si>
-    <t>60.0</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>292.0</t>
-  </si>
-  <si>
-    <t>112.0</t>
-  </si>
-  <si>
-    <t>147.0</t>
+    <t>5.3%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>6.9%</t>
+  </si>
+  <si>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>4.5%</t>
+  </si>
+  <si>
+    <t>1359.0</t>
+  </si>
+  <si>
+    <t>1116.0</t>
+  </si>
+  <si>
+    <t>96.0</t>
+  </si>
+  <si>
+    <t>24.0</t>
+  </si>
+  <si>
+    <t>309.0</t>
+  </si>
+  <si>
+    <t>73.0</t>
+  </si>
+  <si>
+    <t>11.0</t>
+  </si>
+  <si>
+    <t>406.0</t>
+  </si>
+  <si>
+    <t>169.0</t>
+  </si>
+  <si>
+    <t>264.0</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>20.0</t>
+    <t>31.0</t>
   </si>
   <si>
     <t>1</t>
@@ -1899,7 +1899,7 @@
         <v>19505</v>
       </c>
       <c r="B4" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C4" s="4">
         <v>51</v>
@@ -1929,18 +1929,30 @@
         <v>58</v>
       </c>
       <c r="L4" s="4"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="6"/>
+      <c r="M4" s="5">
+        <v>6914.2600000000002</v>
+      </c>
+      <c r="N4" s="6">
+        <v>73</v>
+      </c>
       <c r="O4" s="6">
         <v>53</v>
       </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
+      <c r="P4" s="7">
+        <v>6.3387323943661977</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>17.262264150943395</v>
+      </c>
+      <c r="R4" s="8">
+        <v>5.1635226415094335</v>
+      </c>
       <c r="S4" s="8">
         <v>5.2999999999999998</v>
       </c>
-      <c r="T4" s="9"/>
+      <c r="T4" s="9">
+        <v>0.32075471698113206</v>
+      </c>
       <c r="U4" s="9">
         <v>0.15094339622641509</v>
       </c>
@@ -2330,7 +2342,9 @@
       <c r="N7" s="6">
         <v>68</v>
       </c>
-      <c r="O7" s="6"/>
+      <c r="O7" s="6">
+        <v>34</v>
+      </c>
       <c r="P7" s="7">
         <v>14.057936507936507</v>
       </c>
@@ -2340,31 +2354,75 @@
       <c r="R7" s="8">
         <v>5.2442718749999999</v>
       </c>
-      <c r="S7" s="8"/>
+      <c r="S7" s="8">
+        <v>7</v>
+      </c>
       <c r="T7" s="9">
         <v>0.20588235294117646</v>
       </c>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="9"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
-      <c r="AJ7" s="6"/>
-      <c r="AK7" s="6"/>
-      <c r="AL7" s="6"/>
-      <c r="AM7" s="6"/>
-      <c r="AN7" s="9"/>
-      <c r="AO7" s="6"/>
+      <c r="U7" s="9">
+        <v>0.088235294117647065</v>
+      </c>
+      <c r="V7" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="W7" s="9">
+        <v>0.029411764704999999</v>
+      </c>
+      <c r="X7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE7" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP7" s="4">
         <v>58</v>
       </c>
@@ -2870,7 +2928,7 @@
         <v>19513</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>51</v>
@@ -2900,35 +2958,93 @@
         <v>58</v>
       </c>
       <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="6"/>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="6"/>
-      <c r="AK11" s="6"/>
-      <c r="AL11" s="6"/>
-      <c r="AM11" s="6"/>
-      <c r="AN11" s="9"/>
-      <c r="AO11" s="6"/>
+      <c r="M11" s="5">
+        <v>6446.6599999999999</v>
+      </c>
+      <c r="N11" s="6">
+        <v>63</v>
+      </c>
+      <c r="O11" s="6">
+        <v>41</v>
+      </c>
+      <c r="P11" s="7">
+        <v>5.0190854838709678</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>14.872763414634148</v>
+      </c>
+      <c r="R11" s="8">
+        <v>3.2747975609756095</v>
+      </c>
+      <c r="S11" s="8">
+        <v>6</v>
+      </c>
+      <c r="T11" s="9">
+        <v>0.58536585365853655</v>
+      </c>
+      <c r="U11" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP11" s="4">
         <v>58</v>
       </c>
@@ -3126,7 +3242,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3156,35 +3272,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>7453.8000000000002</v>
+      </c>
+      <c r="N13" s="6">
+        <v>80</v>
+      </c>
+      <c r="O13" s="6">
+        <v>50</v>
+      </c>
+      <c r="P13" s="7">
+        <v>6.0044871794871799</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>20.169665999999999</v>
+      </c>
+      <c r="R13" s="8">
+        <v>7.190334</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0.059999999999999998</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>3</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -3378,7 +3552,7 @@
         <v>19519</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C15" s="4">
         <v>51</v>
@@ -3408,35 +3582,93 @@
         <v>58</v>
       </c>
       <c r="L15" s="4"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
-      <c r="AA15" s="9"/>
-      <c r="AB15" s="9"/>
-      <c r="AC15" s="9"/>
-      <c r="AD15" s="6"/>
-      <c r="AE15" s="6"/>
-      <c r="AF15" s="6"/>
-      <c r="AG15" s="6"/>
-      <c r="AH15" s="6"/>
-      <c r="AI15" s="6"/>
-      <c r="AJ15" s="6"/>
-      <c r="AK15" s="6"/>
-      <c r="AL15" s="6"/>
-      <c r="AM15" s="6"/>
-      <c r="AN15" s="9"/>
-      <c r="AO15" s="6"/>
+      <c r="M15" s="5">
+        <v>14000.030000000001</v>
+      </c>
+      <c r="N15" s="6">
+        <v>162</v>
+      </c>
+      <c r="O15" s="6">
+        <v>71</v>
+      </c>
+      <c r="P15" s="7">
+        <v>4.185683974358974</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>15.503052112676055</v>
+      </c>
+      <c r="R15" s="8">
+        <v>4.0254757142857143</v>
+      </c>
+      <c r="S15" s="8">
+        <v>7</v>
+      </c>
+      <c r="T15" s="9">
+        <v>0.52112676056338025</v>
+      </c>
+      <c r="U15" s="9">
+        <v>0.084507042253521125</v>
+      </c>
+      <c r="V15" s="9">
+        <v>0</v>
+      </c>
+      <c r="W15" s="9">
+        <v>0</v>
+      </c>
+      <c r="X15" s="9">
+        <v>0.056338028169014086</v>
+      </c>
+      <c r="Y15" s="9">
+        <v>0.014084507042253521</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="9">
+        <v>0.014084507042253521</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="9">
+        <v>0.028169014084507043</v>
+      </c>
+      <c r="AD15" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE15" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI15" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP15" s="4">
         <v>58</v>
       </c>
@@ -4139,7 +4371,9 @@
       <c r="N20" s="6">
         <v>101</v>
       </c>
-      <c r="O20" s="6"/>
+      <c r="O20" s="6">
+        <v>68</v>
+      </c>
       <c r="P20" s="7">
         <v>5.9295918367346943</v>
       </c>
@@ -4149,31 +4383,75 @@
       <c r="R20" s="8">
         <v>5.3781867647058821</v>
       </c>
-      <c r="S20" s="8"/>
+      <c r="S20" s="8">
+        <v>7</v>
+      </c>
       <c r="T20" s="9">
         <v>0.30882352941176472</v>
       </c>
-      <c r="U20" s="9"/>
-      <c r="V20" s="9"/>
-      <c r="W20" s="9"/>
-      <c r="X20" s="9"/>
-      <c r="Y20" s="9"/>
-      <c r="Z20" s="9"/>
-      <c r="AA20" s="9"/>
-      <c r="AB20" s="9"/>
-      <c r="AC20" s="9"/>
-      <c r="AD20" s="6"/>
-      <c r="AE20" s="6"/>
-      <c r="AF20" s="6"/>
-      <c r="AG20" s="6"/>
-      <c r="AH20" s="6"/>
-      <c r="AI20" s="6"/>
-      <c r="AJ20" s="6"/>
-      <c r="AK20" s="6"/>
-      <c r="AL20" s="6"/>
-      <c r="AM20" s="6"/>
-      <c r="AN20" s="9"/>
-      <c r="AO20" s="6"/>
+      <c r="U20" s="9">
+        <v>0.10294117647058823</v>
+      </c>
+      <c r="V20" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="W20" s="9">
+        <v>0</v>
+      </c>
+      <c r="X20" s="9">
+        <v>0.073529411764705885</v>
+      </c>
+      <c r="Y20" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE20" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF20" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP20" s="4">
         <v>58</v>
       </c>
@@ -5096,7 +5374,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>51</v>
@@ -5126,35 +5404,93 @@
         <v>58</v>
       </c>
       <c r="L27" s="4"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="6"/>
-      <c r="AK27" s="6"/>
-      <c r="AL27" s="6"/>
-      <c r="AM27" s="6"/>
-      <c r="AN27" s="9"/>
-      <c r="AO27" s="6"/>
+      <c r="M27" s="5">
+        <v>2681.75</v>
+      </c>
+      <c r="N27" s="6">
+        <v>33</v>
+      </c>
+      <c r="O27" s="6">
+        <v>26</v>
+      </c>
+      <c r="P27" s="7">
+        <v>3.555051515151515</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>20.42371923076923</v>
+      </c>
+      <c r="R27" s="8">
+        <v>9.3388875000000002</v>
+      </c>
+      <c r="S27" s="8">
+        <v>8</v>
+      </c>
+      <c r="T27" s="9">
+        <v>0.34615384615384615</v>
+      </c>
+      <c r="U27" s="9">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="V27" s="9">
+        <v>0</v>
+      </c>
+      <c r="W27" s="9">
+        <v>0</v>
+      </c>
+      <c r="X27" s="9">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="Y27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AA27" s="9">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="AB27" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AC27" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AD27" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK27" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM27" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP27" s="4">
         <v>58</v>
       </c>
@@ -5195,7 +5531,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>51</v>
@@ -5225,35 +5561,93 @@
         <v>58</v>
       </c>
       <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="6"/>
-      <c r="AN28" s="9"/>
-      <c r="AO28" s="6"/>
+      <c r="M28" s="5">
+        <v>6722.8699999999999</v>
+      </c>
+      <c r="N28" s="6">
+        <v>63</v>
+      </c>
+      <c r="O28" s="6">
+        <v>33</v>
+      </c>
+      <c r="P28" s="7">
+        <v>3.4491803278688526</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>19.850521874999998</v>
+      </c>
+      <c r="R28" s="8">
+        <v>9.4322906250000003</v>
+      </c>
+      <c r="S28" s="8">
+        <v>7</v>
+      </c>
+      <c r="T28" s="9">
+        <v>0.34375</v>
+      </c>
+      <c r="U28" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="V28" s="9">
+        <v>0</v>
+      </c>
+      <c r="W28" s="9">
+        <v>0</v>
+      </c>
+      <c r="X28" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP28" s="4">
         <v>58</v>
       </c>
@@ -5451,7 +5845,7 @@
         <v>19550</v>
       </c>
       <c r="B30" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C30" s="4">
         <v>51</v>
@@ -5481,35 +5875,93 @@
         <v>58</v>
       </c>
       <c r="L30" s="4"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="7"/>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="W30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="9"/>
-      <c r="AA30" s="9"/>
-      <c r="AB30" s="9"/>
-      <c r="AC30" s="9"/>
-      <c r="AD30" s="6"/>
-      <c r="AE30" s="6"/>
-      <c r="AF30" s="6"/>
-      <c r="AG30" s="6"/>
-      <c r="AH30" s="6"/>
-      <c r="AI30" s="6"/>
-      <c r="AJ30" s="6"/>
-      <c r="AK30" s="6"/>
-      <c r="AL30" s="6"/>
-      <c r="AM30" s="6"/>
-      <c r="AN30" s="9"/>
-      <c r="AO30" s="6"/>
+      <c r="M30" s="5">
+        <v>3264.1799999999998</v>
+      </c>
+      <c r="N30" s="6">
+        <v>30</v>
+      </c>
+      <c r="O30" s="6">
+        <v>13</v>
+      </c>
+      <c r="P30" s="7">
+        <v>2.6161099999999999</v>
+      </c>
+      <c r="Q30" s="8">
+        <v>15.973076923076924</v>
+      </c>
+      <c r="R30" s="8">
+        <v>6.2756384615384615</v>
+      </c>
+      <c r="S30" s="8">
+        <v>7</v>
+      </c>
+      <c r="T30" s="9">
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="U30" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="V30" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="W30" s="9">
+        <v>0</v>
+      </c>
+      <c r="X30" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE30" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP30" s="4">
         <v>58</v>
       </c>
@@ -5586,7 +6038,9 @@
       <c r="N31" s="6">
         <v>49</v>
       </c>
-      <c r="O31" s="6"/>
+      <c r="O31" s="6">
+        <v>31</v>
+      </c>
       <c r="P31" s="7">
         <v>3.2813339999999998</v>
       </c>
@@ -5596,31 +6050,75 @@
       <c r="R31" s="8">
         <v>2.6083333333333334</v>
       </c>
-      <c r="S31" s="8"/>
+      <c r="S31" s="8">
+        <v>8</v>
+      </c>
       <c r="T31" s="9">
         <v>0.67741935483870963</v>
       </c>
-      <c r="U31" s="9"/>
-      <c r="V31" s="9"/>
-      <c r="W31" s="9"/>
-      <c r="X31" s="9"/>
-      <c r="Y31" s="9"/>
-      <c r="Z31" s="9"/>
-      <c r="AA31" s="9"/>
-      <c r="AB31" s="9"/>
-      <c r="AC31" s="9"/>
-      <c r="AD31" s="6"/>
-      <c r="AE31" s="6"/>
-      <c r="AF31" s="6"/>
-      <c r="AG31" s="6"/>
-      <c r="AH31" s="6"/>
-      <c r="AI31" s="6"/>
-      <c r="AJ31" s="6"/>
-      <c r="AK31" s="6"/>
-      <c r="AL31" s="6"/>
-      <c r="AM31" s="6"/>
-      <c r="AN31" s="9"/>
-      <c r="AO31" s="6"/>
+      <c r="U31" s="9">
+        <v>0.19354838709677419</v>
+      </c>
+      <c r="V31" s="9">
+        <v>0</v>
+      </c>
+      <c r="W31" s="9">
+        <v>0</v>
+      </c>
+      <c r="X31" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="9">
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="AB31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE31" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="AO31" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP31" s="4">
         <v>58</v>
       </c>
@@ -5661,7 +6159,7 @@
         <v>19552</v>
       </c>
       <c r="B32" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C32" s="4">
         <v>51</v>
@@ -5691,18 +6189,30 @@
         <v>58</v>
       </c>
       <c r="L32" s="4"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="6"/>
+      <c r="M32" s="5">
+        <v>10130.959999999999</v>
+      </c>
+      <c r="N32" s="6">
+        <v>92</v>
+      </c>
       <c r="O32" s="6">
         <v>65</v>
       </c>
-      <c r="P32" s="7"/>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="8"/>
+      <c r="P32" s="7">
+        <v>2.9344206521739129</v>
+      </c>
+      <c r="Q32" s="8">
+        <v>15.467180000000001</v>
+      </c>
+      <c r="R32" s="8">
+        <v>6.5825515625</v>
+      </c>
       <c r="S32" s="8">
         <v>6</v>
       </c>
-      <c r="T32" s="9"/>
+      <c r="T32" s="9">
+        <v>0.55384615384615388</v>
+      </c>
       <c r="U32" s="9">
         <v>0.076923076923076927</v>
       </c>
@@ -5806,7 +6316,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>51</v>
@@ -5834,35 +6344,93 @@
         <v>58</v>
       </c>
       <c r="L33" s="4"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
-      <c r="S33" s="8"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-      <c r="AA33" s="9"/>
-      <c r="AB33" s="9"/>
-      <c r="AC33" s="9"/>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="6"/>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="6"/>
-      <c r="AK33" s="6"/>
-      <c r="AL33" s="6"/>
-      <c r="AM33" s="6"/>
-      <c r="AN33" s="9"/>
-      <c r="AO33" s="6"/>
+      <c r="M33" s="5">
+        <v>5972.04</v>
+      </c>
+      <c r="N33" s="6">
+        <v>46</v>
+      </c>
+      <c r="O33" s="6">
+        <v>20</v>
+      </c>
+      <c r="P33" s="7">
+        <v>1.9612326086956522</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>15.395</v>
+      </c>
+      <c r="R33" s="8">
+        <v>6.4950000000000001</v>
+      </c>
+      <c r="S33" s="8">
+        <v>7</v>
+      </c>
+      <c r="T33" s="9">
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="U33" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="V33" s="9">
+        <v>0</v>
+      </c>
+      <c r="W33" s="9">
+        <v>0</v>
+      </c>
+      <c r="X33" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y33" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP33" s="4">
         <v>58</v>
       </c>
@@ -5903,7 +6471,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>51</v>
@@ -5933,35 +6501,93 @@
         <v>58</v>
       </c>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-      <c r="O34" s="6"/>
-      <c r="P34" s="7"/>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="8"/>
-      <c r="T34" s="9"/>
-      <c r="U34" s="9"/>
-      <c r="V34" s="9"/>
-      <c r="W34" s="9"/>
-      <c r="X34" s="9"/>
-      <c r="Y34" s="9"/>
-      <c r="Z34" s="9"/>
-      <c r="AA34" s="9"/>
-      <c r="AB34" s="9"/>
-      <c r="AC34" s="9"/>
-      <c r="AD34" s="6"/>
-      <c r="AE34" s="6"/>
-      <c r="AF34" s="6"/>
-      <c r="AG34" s="6"/>
-      <c r="AH34" s="6"/>
-      <c r="AI34" s="6"/>
-      <c r="AJ34" s="6"/>
-      <c r="AK34" s="6"/>
-      <c r="AL34" s="6"/>
-      <c r="AM34" s="6"/>
-      <c r="AN34" s="9"/>
-      <c r="AO34" s="6"/>
+      <c r="M34" s="5">
+        <v>9233.4300000000003</v>
+      </c>
+      <c r="N34" s="6">
+        <v>103</v>
+      </c>
+      <c r="O34" s="6">
+        <v>76</v>
+      </c>
+      <c r="P34" s="7">
+        <v>7.8630715686274515</v>
+      </c>
+      <c r="Q34" s="8">
+        <v>15.946930263157894</v>
+      </c>
+      <c r="R34" s="8">
+        <v>1.6407402777777778</v>
+      </c>
+      <c r="S34" s="8">
+        <v>6</v>
+      </c>
+      <c r="T34" s="9">
+        <v>0.53947368421052633</v>
+      </c>
+      <c r="U34" s="9">
+        <v>0.19736842105263158</v>
+      </c>
+      <c r="V34" s="9">
+        <v>0</v>
+      </c>
+      <c r="W34" s="9">
+        <v>0</v>
+      </c>
+      <c r="X34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="9">
+        <v>0.14473684210526316</v>
+      </c>
+      <c r="AB34" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="AC34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="6">
+        <v>15</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="6">
+        <v>11</v>
+      </c>
+      <c r="AL34" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM34" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP34" s="4">
         <v>58</v>
       </c>
@@ -6256,7 +6882,7 @@
         <v>19563</v>
       </c>
       <c r="B37" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C37" s="4">
         <v>51</v>
@@ -6286,18 +6912,30 @@
         <v>58</v>
       </c>
       <c r="L37" s="4"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="6"/>
+      <c r="M37" s="5">
+        <v>4753.3500000000004</v>
+      </c>
+      <c r="N37" s="6">
+        <v>53</v>
+      </c>
       <c r="O37" s="6">
         <v>28</v>
       </c>
-      <c r="P37" s="7"/>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="8"/>
+      <c r="P37" s="7">
+        <v>3.6854944444444442</v>
+      </c>
+      <c r="Q37" s="8">
+        <v>20.783928571428572</v>
+      </c>
+      <c r="R37" s="8">
+        <v>11.376923076923077</v>
+      </c>
       <c r="S37" s="8">
         <v>7</v>
       </c>
-      <c r="T37" s="9"/>
+      <c r="T37" s="9">
+        <v>0.32142857142857145</v>
+      </c>
       <c r="U37" s="9">
         <v>0.4642857142857143</v>
       </c>
@@ -6558,7 +7196,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -6588,35 +7226,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>4321</v>
+      </c>
+      <c r="N39" s="6">
+        <v>45</v>
+      </c>
+      <c r="O39" s="6">
+        <v>26</v>
+      </c>
+      <c r="P39" s="7">
+        <v>1.9855555555555555</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>11.594230769230769</v>
+      </c>
+      <c r="R39" s="8">
+        <v>4.3999999999999995</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.80769230769230771</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>19</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>10</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -6971,7 +7667,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7001,35 +7697,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>4911.6300000000001</v>
+      </c>
+      <c r="N42" s="6">
+        <v>48</v>
+      </c>
+      <c r="O42" s="6">
+        <v>35</v>
+      </c>
+      <c r="P42" s="7">
+        <v>6.0235500000000002</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>21.842379999999999</v>
+      </c>
+      <c r="R42" s="8">
+        <v>8.9328571428571415</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -7541,7 +8295,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>51</v>
@@ -7569,35 +8323,93 @@
         <v>58</v>
       </c>
       <c r="L46" s="4"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="8"/>
-      <c r="R46" s="8"/>
-      <c r="S46" s="8"/>
-      <c r="T46" s="9"/>
-      <c r="U46" s="9"/>
-      <c r="V46" s="9"/>
-      <c r="W46" s="9"/>
-      <c r="X46" s="9"/>
-      <c r="Y46" s="9"/>
-      <c r="Z46" s="9"/>
-      <c r="AA46" s="9"/>
-      <c r="AB46" s="9"/>
-      <c r="AC46" s="9"/>
-      <c r="AD46" s="6"/>
-      <c r="AE46" s="6"/>
-      <c r="AF46" s="6"/>
-      <c r="AG46" s="6"/>
-      <c r="AH46" s="6"/>
-      <c r="AI46" s="6"/>
-      <c r="AJ46" s="6"/>
-      <c r="AK46" s="6"/>
-      <c r="AL46" s="6"/>
-      <c r="AM46" s="6"/>
-      <c r="AN46" s="9"/>
-      <c r="AO46" s="6"/>
+      <c r="M46" s="5">
+        <v>7533.7600000000002</v>
+      </c>
+      <c r="N46" s="6">
+        <v>65</v>
+      </c>
+      <c r="O46" s="6">
+        <v>33</v>
+      </c>
+      <c r="P46" s="7">
+        <v>7.660512307692307</v>
+      </c>
+      <c r="Q46" s="8">
+        <v>31.326263636363635</v>
+      </c>
+      <c r="R46" s="8">
+        <v>15.555912903225806</v>
+      </c>
+      <c r="S46" s="8">
+        <v>7</v>
+      </c>
+      <c r="T46" s="9">
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="U46" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="V46" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="W46" s="9">
+        <v>0</v>
+      </c>
+      <c r="X46" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="Y46" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="AA46" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="AB46" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="AC46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF46" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK46" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL46" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM46" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN46" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP46" s="4">
         <v>58</v>
       </c>
@@ -8105,7 +8917,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>51</v>
@@ -8135,35 +8947,93 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="6"/>
+      <c r="M50" s="5">
+        <v>4772.2200000000003</v>
+      </c>
+      <c r="N50" s="6">
+        <v>60</v>
+      </c>
+      <c r="O50" s="6">
+        <v>38</v>
+      </c>
+      <c r="P50" s="7">
+        <v>2.7612127272727274</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>17.832018421052634</v>
+      </c>
+      <c r="R50" s="8">
+        <v>7.0964921052631578</v>
+      </c>
+      <c r="S50" s="8">
+        <v>8</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0.55263157894736847</v>
+      </c>
+      <c r="U50" s="9">
+        <v>0.21052631578947367</v>
+      </c>
+      <c r="V50" s="9">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0.026315789472999999</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="9">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="AB50" s="9">
+        <v>0.13157894736842105</v>
+      </c>
+      <c r="AC50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP50" s="4">
         <v>58</v>
       </c>
@@ -8303,7 +9173,7 @@
         <v>19606</v>
       </c>
       <c r="B52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C52" s="4">
         <v>51</v>
@@ -8333,35 +9203,93 @@
         <v>58</v>
       </c>
       <c r="L52" s="4"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="8"/>
-      <c r="R52" s="8"/>
-      <c r="S52" s="8"/>
-      <c r="T52" s="9"/>
-      <c r="U52" s="9"/>
-      <c r="V52" s="9"/>
-      <c r="W52" s="9"/>
-      <c r="X52" s="9"/>
-      <c r="Y52" s="9"/>
-      <c r="Z52" s="9"/>
-      <c r="AA52" s="9"/>
-      <c r="AB52" s="9"/>
-      <c r="AC52" s="9"/>
-      <c r="AD52" s="6"/>
-      <c r="AE52" s="6"/>
-      <c r="AF52" s="6"/>
-      <c r="AG52" s="6"/>
-      <c r="AH52" s="6"/>
-      <c r="AI52" s="6"/>
-      <c r="AJ52" s="6"/>
-      <c r="AK52" s="6"/>
-      <c r="AL52" s="6"/>
-      <c r="AM52" s="6"/>
-      <c r="AN52" s="9"/>
-      <c r="AO52" s="6"/>
+      <c r="M52" s="5">
+        <v>3665.3000000000002</v>
+      </c>
+      <c r="N52" s="6">
+        <v>41</v>
+      </c>
+      <c r="O52" s="6">
+        <v>17</v>
+      </c>
+      <c r="P52" s="7">
+        <v>5.6531000000000002</v>
+      </c>
+      <c r="Q52" s="8">
+        <v>16.288235294117644</v>
+      </c>
+      <c r="R52" s="8">
+        <v>2.693135294117647</v>
+      </c>
+      <c r="S52" s="8">
+        <v>8</v>
+      </c>
+      <c r="T52" s="9">
+        <v>0.35294117647058826</v>
+      </c>
+      <c r="U52" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="V52" s="9">
+        <v>0</v>
+      </c>
+      <c r="W52" s="9">
+        <v>0</v>
+      </c>
+      <c r="X52" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AB52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE52" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP52" s="4">
         <v>58</v>
       </c>
@@ -8436,7 +9364,9 @@
       <c r="N53" s="6">
         <v>55</v>
       </c>
-      <c r="O53" s="6"/>
+      <c r="O53" s="6">
+        <v>25</v>
+      </c>
       <c r="P53" s="7">
         <v>2.7043203703703704</v>
       </c>
@@ -8446,31 +9376,75 @@
       <c r="R53" s="8">
         <v>2.7480000000000002</v>
       </c>
-      <c r="S53" s="8"/>
+      <c r="S53" s="8">
+        <v>7</v>
+      </c>
       <c r="T53" s="9">
         <v>0.92000000000000004</v>
       </c>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
-      <c r="X53" s="9"/>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
-      <c r="AA53" s="9"/>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="6"/>
-      <c r="AM53" s="6"/>
-      <c r="AN53" s="9"/>
-      <c r="AO53" s="6"/>
+      <c r="U53" s="9">
+        <v>0</v>
+      </c>
+      <c r="V53" s="9">
+        <v>0</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP53" s="4">
         <v>58</v>
       </c>
@@ -8668,7 +9642,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -8698,35 +9672,93 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="M55" s="5">
+        <v>5339</v>
+      </c>
+      <c r="N55" s="6">
+        <v>56</v>
+      </c>
+      <c r="O55" s="6">
+        <v>41</v>
+      </c>
+      <c r="P55" s="7">
+        <v>2.8415145454545452</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>20.304167499999998</v>
+      </c>
+      <c r="R55" s="8">
+        <v>10.4475</v>
+      </c>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
+      <c r="T55" s="9">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="U55" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0.04878048780487805</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -9079,7 +10111,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -9109,35 +10141,93 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
-      <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="M58" s="5">
+        <v>4712.8699999999999</v>
+      </c>
+      <c r="N58" s="6">
+        <v>56</v>
+      </c>
+      <c r="O58" s="6">
+        <v>42</v>
+      </c>
+      <c r="P58" s="7">
+        <v>2.9772727272727271</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>17.361904761904764</v>
+      </c>
+      <c r="R58" s="8">
+        <v>7.1535714285714285</v>
+      </c>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
+      <c r="T58" s="9">
+        <v>0.40476190476190477</v>
+      </c>
+      <c r="U58" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -9645,7 +10735,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>51</v>
@@ -9675,35 +10765,93 @@
         <v>58</v>
       </c>
       <c r="L62" s="4"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="6"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="8"/>
-      <c r="R62" s="8"/>
-      <c r="S62" s="8"/>
-      <c r="T62" s="9"/>
-      <c r="U62" s="9"/>
-      <c r="V62" s="9"/>
-      <c r="W62" s="9"/>
-      <c r="X62" s="9"/>
-      <c r="Y62" s="9"/>
-      <c r="Z62" s="9"/>
-      <c r="AA62" s="9"/>
-      <c r="AB62" s="9"/>
-      <c r="AC62" s="9"/>
-      <c r="AD62" s="6"/>
-      <c r="AE62" s="6"/>
-      <c r="AF62" s="6"/>
-      <c r="AG62" s="6"/>
-      <c r="AH62" s="6"/>
-      <c r="AI62" s="6"/>
-      <c r="AJ62" s="6"/>
-      <c r="AK62" s="6"/>
-      <c r="AL62" s="6"/>
-      <c r="AM62" s="6"/>
-      <c r="AN62" s="9"/>
-      <c r="AO62" s="6"/>
+      <c r="M62" s="5">
+        <v>5649.6300000000001</v>
+      </c>
+      <c r="N62" s="6">
+        <v>53</v>
+      </c>
+      <c r="O62" s="6">
+        <v>30</v>
+      </c>
+      <c r="P62" s="7">
+        <v>2.8962264150943398</v>
+      </c>
+      <c r="Q62" s="8">
+        <v>14.317776666666667</v>
+      </c>
+      <c r="R62" s="8">
+        <v>4.2516666666666669</v>
+      </c>
+      <c r="S62" s="8">
+        <v>7</v>
+      </c>
+      <c r="T62" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U62" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="V62" s="9">
+        <v>0</v>
+      </c>
+      <c r="W62" s="9">
+        <v>0</v>
+      </c>
+      <c r="X62" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="Y62" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AB62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP62" s="4">
         <v>58</v>
       </c>
@@ -10191,7 +11339,9 @@
       <c r="N66" s="6">
         <v>51</v>
       </c>
-      <c r="O66" s="6"/>
+      <c r="O66" s="6">
+        <v>31</v>
+      </c>
       <c r="P66" s="7">
         <v>4.3731891304347821</v>
       </c>
@@ -10201,31 +11351,75 @@
       <c r="R66" s="8">
         <v>8.1446428571428573</v>
       </c>
-      <c r="S66" s="8"/>
+      <c r="S66" s="8">
+        <v>7</v>
+      </c>
       <c r="T66" s="9">
         <v>0.5161290322580645</v>
       </c>
-      <c r="U66" s="9"/>
-      <c r="V66" s="9"/>
-      <c r="W66" s="9"/>
-      <c r="X66" s="9"/>
-      <c r="Y66" s="9"/>
-      <c r="Z66" s="9"/>
-      <c r="AA66" s="9"/>
-      <c r="AB66" s="9"/>
-      <c r="AC66" s="9"/>
-      <c r="AD66" s="6"/>
-      <c r="AE66" s="6"/>
-      <c r="AF66" s="6"/>
-      <c r="AG66" s="6"/>
-      <c r="AH66" s="6"/>
-      <c r="AI66" s="6"/>
-      <c r="AJ66" s="6"/>
-      <c r="AK66" s="6"/>
-      <c r="AL66" s="6"/>
-      <c r="AM66" s="6"/>
-      <c r="AN66" s="9"/>
-      <c r="AO66" s="6"/>
+      <c r="U66" s="9">
+        <v>0.19354838709677419</v>
+      </c>
+      <c r="V66" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="W66" s="9">
+        <v>0</v>
+      </c>
+      <c r="X66" s="9">
+        <v>0.096774193548387094</v>
+      </c>
+      <c r="Y66" s="9">
+        <v>0.096774193548387094</v>
+      </c>
+      <c r="Z66" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="9">
+        <v>0.096774193548387094</v>
+      </c>
+      <c r="AB66" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="AC66" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD66" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE66" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF66" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG66" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH66" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI66" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ66" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK66" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL66" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM66" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN66" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="AO66" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP66" s="4">
         <v>58</v>
       </c>
@@ -10890,7 +12084,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>51</v>
@@ -10918,35 +12112,93 @@
         <v>58</v>
       </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-      <c r="AA71" s="9"/>
-      <c r="AB71" s="9"/>
-      <c r="AC71" s="9"/>
-      <c r="AD71" s="6"/>
-      <c r="AE71" s="6"/>
-      <c r="AF71" s="6"/>
-      <c r="AG71" s="6"/>
-      <c r="AH71" s="6"/>
-      <c r="AI71" s="6"/>
-      <c r="AJ71" s="6"/>
-      <c r="AK71" s="6"/>
-      <c r="AL71" s="6"/>
-      <c r="AM71" s="6"/>
-      <c r="AN71" s="9"/>
-      <c r="AO71" s="6"/>
+      <c r="M71" s="5">
+        <v>4609.3500000000004</v>
+      </c>
+      <c r="N71" s="6">
+        <v>55</v>
+      </c>
+      <c r="O71" s="6">
+        <v>20</v>
+      </c>
+      <c r="P71" s="7">
+        <v>2.8643784313725491</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>14.98</v>
+      </c>
+      <c r="R71" s="8">
+        <v>4.211665</v>
+      </c>
+      <c r="S71" s="8">
+        <v>8</v>
+      </c>
+      <c r="T71" s="9">
+        <v>0.45000000000000001</v>
+      </c>
+      <c r="U71" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP71" s="4">
         <v>58</v>
       </c>
@@ -11394,7 +12646,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -11424,35 +12676,93 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="M75" s="5">
+        <v>3890.3200000000002</v>
+      </c>
+      <c r="N75" s="6">
+        <v>43</v>
+      </c>
+      <c r="O75" s="6">
+        <v>24</v>
+      </c>
+      <c r="P75" s="7">
+        <v>5.3511363636363631</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>21.650000000000002</v>
+      </c>
+      <c r="R75" s="8">
+        <v>9.0905782608695649</v>
+      </c>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.20833333333333334</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -11493,7 +12803,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -11521,35 +12831,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>6346.4200000000001</v>
+      </c>
+      <c r="N76" s="6">
+        <v>78</v>
+      </c>
+      <c r="O76" s="6">
+        <v>45</v>
+      </c>
+      <c r="P76" s="7">
+        <v>2.6567103896103896</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>16.635555555555555</v>
+      </c>
+      <c r="R76" s="8">
+        <v>5.5174804878048782</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.48888888888888887</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.044444444444444446</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.044444444444444446</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>17</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -11745,7 +13113,7 @@
         <v>19666</v>
       </c>
       <c r="B78" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C78" s="4">
         <v>51</v>
@@ -11773,35 +13141,93 @@
         <v>58</v>
       </c>
       <c r="L78" s="4"/>
-      <c r="M78" s="5"/>
-      <c r="N78" s="6"/>
-      <c r="O78" s="6"/>
-      <c r="P78" s="7"/>
-      <c r="Q78" s="8"/>
-      <c r="R78" s="8"/>
-      <c r="S78" s="8"/>
-      <c r="T78" s="9"/>
-      <c r="U78" s="9"/>
-      <c r="V78" s="9"/>
-      <c r="W78" s="9"/>
-      <c r="X78" s="9"/>
-      <c r="Y78" s="9"/>
-      <c r="Z78" s="9"/>
-      <c r="AA78" s="9"/>
-      <c r="AB78" s="9"/>
-      <c r="AC78" s="9"/>
-      <c r="AD78" s="6"/>
-      <c r="AE78" s="6"/>
-      <c r="AF78" s="6"/>
-      <c r="AG78" s="6"/>
-      <c r="AH78" s="6"/>
-      <c r="AI78" s="6"/>
-      <c r="AJ78" s="6"/>
-      <c r="AK78" s="6"/>
-      <c r="AL78" s="6"/>
-      <c r="AM78" s="6"/>
-      <c r="AN78" s="9"/>
-      <c r="AO78" s="6"/>
+      <c r="M78" s="5">
+        <v>6288.3900000000003</v>
+      </c>
+      <c r="N78" s="6">
+        <v>57</v>
+      </c>
+      <c r="O78" s="6">
+        <v>45</v>
+      </c>
+      <c r="P78" s="7">
+        <v>3.1035714285714286</v>
+      </c>
+      <c r="Q78" s="8">
+        <v>15.213704444444446</v>
+      </c>
+      <c r="R78" s="8">
+        <v>4.0818511111111109</v>
+      </c>
+      <c r="S78" s="8">
+        <v>8</v>
+      </c>
+      <c r="T78" s="9">
+        <v>0.51111111111111107</v>
+      </c>
+      <c r="U78" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="V78" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="W78" s="9">
+        <v>0.022222222222000002</v>
+      </c>
+      <c r="X78" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="Y78" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="AC78" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE78" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF78" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG78" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH78" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL78" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM78" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN78" s="9">
+        <v>0.044444444444444446</v>
+      </c>
+      <c r="AO78" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP78" s="4">
         <v>58</v>
       </c>
@@ -12567,7 +13993,7 @@
         <v>19685</v>
       </c>
       <c r="B84" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C84" s="4">
         <v>51</v>
@@ -12597,35 +14023,93 @@
         <v>58</v>
       </c>
       <c r="L84" s="4"/>
-      <c r="M84" s="5"/>
-      <c r="N84" s="6"/>
-      <c r="O84" s="6"/>
-      <c r="P84" s="7"/>
-      <c r="Q84" s="8"/>
-      <c r="R84" s="8"/>
-      <c r="S84" s="8"/>
-      <c r="T84" s="9"/>
-      <c r="U84" s="9"/>
-      <c r="V84" s="9"/>
-      <c r="W84" s="9"/>
-      <c r="X84" s="9"/>
-      <c r="Y84" s="9"/>
-      <c r="Z84" s="9"/>
-      <c r="AA84" s="9"/>
-      <c r="AB84" s="9"/>
-      <c r="AC84" s="9"/>
-      <c r="AD84" s="6"/>
-      <c r="AE84" s="6"/>
-      <c r="AF84" s="6"/>
-      <c r="AG84" s="6"/>
-      <c r="AH84" s="6"/>
-      <c r="AI84" s="6"/>
-      <c r="AJ84" s="6"/>
-      <c r="AK84" s="6"/>
-      <c r="AL84" s="6"/>
-      <c r="AM84" s="6"/>
-      <c r="AN84" s="9"/>
-      <c r="AO84" s="6"/>
+      <c r="M84" s="5">
+        <v>3757.9000000000001</v>
+      </c>
+      <c r="N84" s="6">
+        <v>42</v>
+      </c>
+      <c r="O84" s="6">
+        <v>27</v>
+      </c>
+      <c r="P84" s="7">
+        <v>5.9753795454545449</v>
+      </c>
+      <c r="Q84" s="8">
+        <v>33.970370370370375</v>
+      </c>
+      <c r="R84" s="8">
+        <v>23.399332000000001</v>
+      </c>
+      <c r="S84" s="8">
+        <v>7</v>
+      </c>
+      <c r="T84" s="9">
+        <v>0.25925925925925924</v>
+      </c>
+      <c r="U84" s="9">
+        <v>0.14814814814814814</v>
+      </c>
+      <c r="V84" s="9">
+        <v>0</v>
+      </c>
+      <c r="W84" s="9">
+        <v>0</v>
+      </c>
+      <c r="X84" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="Y84" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AB84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE84" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP84" s="4">
         <v>58</v>
       </c>
@@ -12823,7 +14307,7 @@
         <v>19688</v>
       </c>
       <c r="B86" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C86" s="4">
         <v>51</v>
@@ -12853,18 +14337,30 @@
         <v>58</v>
       </c>
       <c r="L86" s="4"/>
-      <c r="M86" s="5"/>
-      <c r="N86" s="6"/>
+      <c r="M86" s="5">
+        <v>3945.3000000000002</v>
+      </c>
+      <c r="N86" s="6">
+        <v>45</v>
+      </c>
       <c r="O86" s="6">
         <v>26</v>
       </c>
-      <c r="P86" s="7"/>
-      <c r="Q86" s="8"/>
-      <c r="R86" s="8"/>
+      <c r="P86" s="7">
+        <v>9.901851111111112</v>
+      </c>
+      <c r="Q86" s="8">
+        <v>21.110896153846152</v>
+      </c>
+      <c r="R86" s="8">
+        <v>3.7680541666666669</v>
+      </c>
       <c r="S86" s="8">
         <v>8.5</v>
       </c>
-      <c r="T86" s="9"/>
+      <c r="T86" s="9">
+        <v>0.11538461538461539</v>
+      </c>
       <c r="U86" s="9">
         <v>0.15384615384615385</v>
       </c>
@@ -13377,7 +14873,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>51</v>
@@ -13407,35 +14903,93 @@
         <v>58</v>
       </c>
       <c r="L90" s="4"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="6"/>
-      <c r="O90" s="6"/>
-      <c r="P90" s="7"/>
-      <c r="Q90" s="8"/>
-      <c r="R90" s="8"/>
-      <c r="S90" s="8"/>
-      <c r="T90" s="9"/>
-      <c r="U90" s="9"/>
-      <c r="V90" s="9"/>
-      <c r="W90" s="9"/>
-      <c r="X90" s="9"/>
-      <c r="Y90" s="9"/>
-      <c r="Z90" s="9"/>
-      <c r="AA90" s="9"/>
-      <c r="AB90" s="9"/>
-      <c r="AC90" s="9"/>
-      <c r="AD90" s="6"/>
-      <c r="AE90" s="6"/>
-      <c r="AF90" s="6"/>
-      <c r="AG90" s="6"/>
-      <c r="AH90" s="6"/>
-      <c r="AI90" s="6"/>
-      <c r="AJ90" s="6"/>
-      <c r="AK90" s="6"/>
-      <c r="AL90" s="6"/>
-      <c r="AM90" s="6"/>
-      <c r="AN90" s="9"/>
-      <c r="AO90" s="6"/>
+      <c r="M90" s="5">
+        <v>4352.5200000000004</v>
+      </c>
+      <c r="N90" s="6">
+        <v>48</v>
+      </c>
+      <c r="O90" s="6">
+        <v>29</v>
+      </c>
+      <c r="P90" s="7">
+        <v>7.893972340425532</v>
+      </c>
+      <c r="Q90" s="8">
+        <v>22.480458620689657</v>
+      </c>
+      <c r="R90" s="8">
+        <v>7.4934535714285717</v>
+      </c>
+      <c r="S90" s="8">
+        <v>7</v>
+      </c>
+      <c r="T90" s="9">
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="U90" s="9">
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="V90" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="W90" s="9">
+        <v>0.068965517241000002</v>
+      </c>
+      <c r="X90" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Y90" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Z90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AB90" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="AC90" s="9">
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="AD90" s="6">
+        <v>11</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF90" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG90" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL90" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM90" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO90" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP90" s="4">
         <v>58</v>
       </c>
@@ -13977,7 +15531,9 @@
       <c r="N94" s="6">
         <v>40</v>
       </c>
-      <c r="O94" s="6"/>
+      <c r="O94" s="6">
+        <v>18</v>
+      </c>
       <c r="P94" s="7">
         <v>5.1108324999999999</v>
       </c>
@@ -13987,31 +15543,75 @@
       <c r="R94" s="8">
         <v>4.4011928571428571</v>
       </c>
-      <c r="S94" s="8"/>
+      <c r="S94" s="8">
+        <v>8</v>
+      </c>
       <c r="T94" s="9">
         <v>0.44444444444444442</v>
       </c>
-      <c r="U94" s="9"/>
-      <c r="V94" s="9"/>
-      <c r="W94" s="9"/>
-      <c r="X94" s="9"/>
-      <c r="Y94" s="9"/>
-      <c r="Z94" s="9"/>
-      <c r="AA94" s="9"/>
-      <c r="AB94" s="9"/>
-      <c r="AC94" s="9"/>
-      <c r="AD94" s="6"/>
-      <c r="AE94" s="6"/>
-      <c r="AF94" s="6"/>
-      <c r="AG94" s="6"/>
-      <c r="AH94" s="6"/>
-      <c r="AI94" s="6"/>
-      <c r="AJ94" s="6"/>
-      <c r="AK94" s="6"/>
-      <c r="AL94" s="6"/>
-      <c r="AM94" s="6"/>
-      <c r="AN94" s="9"/>
-      <c r="AO94" s="6"/>
+      <c r="U94" s="9">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="V94" s="9">
+        <v>0</v>
+      </c>
+      <c r="W94" s="9">
+        <v>0</v>
+      </c>
+      <c r="X94" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA94" s="9">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="AB94" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN94" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO94" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP94" s="4">
         <v>58</v>
       </c>
@@ -15657,7 +17257,7 @@
         <v>19725</v>
       </c>
       <c r="B106" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C106" s="4">
         <v>51</v>
@@ -15687,35 +17287,93 @@
         <v>58</v>
       </c>
       <c r="L106" s="4"/>
-      <c r="M106" s="5"/>
-      <c r="N106" s="6"/>
-      <c r="O106" s="6"/>
-      <c r="P106" s="7"/>
-      <c r="Q106" s="8"/>
-      <c r="R106" s="8"/>
-      <c r="S106" s="8"/>
-      <c r="T106" s="9"/>
-      <c r="U106" s="9"/>
-      <c r="V106" s="9"/>
-      <c r="W106" s="9"/>
-      <c r="X106" s="9"/>
-      <c r="Y106" s="9"/>
-      <c r="Z106" s="9"/>
-      <c r="AA106" s="9"/>
-      <c r="AB106" s="9"/>
-      <c r="AC106" s="9"/>
-      <c r="AD106" s="6"/>
-      <c r="AE106" s="6"/>
-      <c r="AF106" s="6"/>
-      <c r="AG106" s="6"/>
-      <c r="AH106" s="6"/>
-      <c r="AI106" s="6"/>
-      <c r="AJ106" s="6"/>
-      <c r="AK106" s="6"/>
-      <c r="AL106" s="6"/>
-      <c r="AM106" s="6"/>
-      <c r="AN106" s="9"/>
-      <c r="AO106" s="6"/>
+      <c r="M106" s="5">
+        <v>2791.9899999999998</v>
+      </c>
+      <c r="N106" s="6">
+        <v>38</v>
+      </c>
+      <c r="O106" s="6">
+        <v>22</v>
+      </c>
+      <c r="P106" s="7">
+        <v>3.2723684210526316</v>
+      </c>
+      <c r="Q106" s="8">
+        <v>11.427272727272728</v>
+      </c>
+      <c r="R106" s="8">
+        <v>1.6606045454545453</v>
+      </c>
+      <c r="S106" s="8">
+        <v>7</v>
+      </c>
+      <c r="T106" s="9">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="U106" s="9">
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="V106" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="W106" s="9">
+        <v>0</v>
+      </c>
+      <c r="X106" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="Y106" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z106" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA106" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB106" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC106" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD106" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE106" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF106" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG106" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH106" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI106" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ106" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK106" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL106" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM106" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN106" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO106" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP106" s="4">
         <v>58</v>
       </c>
@@ -15756,7 +17414,7 @@
         <v>19727</v>
       </c>
       <c r="B107" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C107" s="4">
         <v>51</v>
@@ -15786,35 +17444,93 @@
         <v>58</v>
       </c>
       <c r="L107" s="4"/>
-      <c r="M107" s="5"/>
-      <c r="N107" s="6"/>
-      <c r="O107" s="6"/>
-      <c r="P107" s="7"/>
-      <c r="Q107" s="8"/>
-      <c r="R107" s="8"/>
-      <c r="S107" s="8"/>
-      <c r="T107" s="9"/>
-      <c r="U107" s="9"/>
-      <c r="V107" s="9"/>
-      <c r="W107" s="9"/>
-      <c r="X107" s="9"/>
-      <c r="Y107" s="9"/>
-      <c r="Z107" s="9"/>
-      <c r="AA107" s="9"/>
-      <c r="AB107" s="9"/>
-      <c r="AC107" s="9"/>
-      <c r="AD107" s="6"/>
-      <c r="AE107" s="6"/>
-      <c r="AF107" s="6"/>
-      <c r="AG107" s="6"/>
-      <c r="AH107" s="6"/>
-      <c r="AI107" s="6"/>
-      <c r="AJ107" s="6"/>
-      <c r="AK107" s="6"/>
-      <c r="AL107" s="6"/>
-      <c r="AM107" s="6"/>
-      <c r="AN107" s="9"/>
-      <c r="AO107" s="6"/>
+      <c r="M107" s="5">
+        <v>2696.1399999999999</v>
+      </c>
+      <c r="N107" s="6">
+        <v>32</v>
+      </c>
+      <c r="O107" s="6">
+        <v>17</v>
+      </c>
+      <c r="P107" s="7">
+        <v>7.9927766666666669</v>
+      </c>
+      <c r="Q107" s="8">
+        <v>20.5</v>
+      </c>
+      <c r="R107" s="8">
+        <v>4.3284294117647057</v>
+      </c>
+      <c r="S107" s="8">
+        <v>7</v>
+      </c>
+      <c r="T107" s="9">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="U107" s="9">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="V107" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="W107" s="9">
+        <v>0</v>
+      </c>
+      <c r="X107" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y107" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z107" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA107" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AB107" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AC107" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD107" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE107" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF107" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK107" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL107" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM107" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN107" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AO107" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP107" s="4">
         <v>58</v>
       </c>
@@ -15954,7 +17670,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>51</v>
@@ -15982,35 +17698,93 @@
         <v>58</v>
       </c>
       <c r="L109" s="4"/>
-      <c r="M109" s="5"/>
-      <c r="N109" s="6"/>
-      <c r="O109" s="6"/>
-      <c r="P109" s="7"/>
-      <c r="Q109" s="8"/>
-      <c r="R109" s="8"/>
-      <c r="S109" s="8"/>
-      <c r="T109" s="9"/>
-      <c r="U109" s="9"/>
-      <c r="V109" s="9"/>
-      <c r="W109" s="9"/>
-      <c r="X109" s="9"/>
-      <c r="Y109" s="9"/>
-      <c r="Z109" s="9"/>
-      <c r="AA109" s="9"/>
-      <c r="AB109" s="9"/>
-      <c r="AC109" s="9"/>
-      <c r="AD109" s="6"/>
-      <c r="AE109" s="6"/>
-      <c r="AF109" s="6"/>
-      <c r="AG109" s="6"/>
-      <c r="AH109" s="6"/>
-      <c r="AI109" s="6"/>
-      <c r="AJ109" s="6"/>
-      <c r="AK109" s="6"/>
-      <c r="AL109" s="6"/>
-      <c r="AM109" s="6"/>
-      <c r="AN109" s="9"/>
-      <c r="AO109" s="6"/>
+      <c r="M109" s="5">
+        <v>4617.7399999999998</v>
+      </c>
+      <c r="N109" s="6">
+        <v>43</v>
+      </c>
+      <c r="O109" s="6">
+        <v>10</v>
+      </c>
+      <c r="P109" s="7">
+        <v>4.0403093023255821</v>
+      </c>
+      <c r="Q109" s="8">
+        <v>16.315000000000001</v>
+      </c>
+      <c r="R109" s="8">
+        <v>3.96</v>
+      </c>
+      <c r="S109" s="8">
+        <v>8</v>
+      </c>
+      <c r="T109" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="U109" s="9">
+        <v>0.69999999999999996</v>
+      </c>
+      <c r="V109" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="W109" s="9">
+        <v>0</v>
+      </c>
+      <c r="X109" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="9">
+        <v>0.29999999999999999</v>
+      </c>
+      <c r="AC109" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="AD109" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF109" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL109" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM109" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO109" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP109" s="4">
         <v>58</v>
       </c>
@@ -16150,7 +17924,7 @@
         <v>19735</v>
       </c>
       <c r="B111" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C111" s="4">
         <v>51</v>
@@ -16180,35 +17954,93 @@
         <v>58</v>
       </c>
       <c r="L111" s="4"/>
-      <c r="M111" s="5"/>
-      <c r="N111" s="6"/>
-      <c r="O111" s="6"/>
-      <c r="P111" s="7"/>
-      <c r="Q111" s="8"/>
-      <c r="R111" s="8"/>
-      <c r="S111" s="8"/>
-      <c r="T111" s="9"/>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="M111" s="5">
+        <v>369.5</v>
+      </c>
+      <c r="N111" s="6">
+        <v>4</v>
+      </c>
+      <c r="O111" s="6">
+        <v>4</v>
+      </c>
+      <c r="P111" s="7">
+        <v>4.3875000000000002</v>
+      </c>
+      <c r="Q111" s="8">
+        <v>12.324999999999999</v>
+      </c>
+      <c r="R111" s="8">
+        <v>1.0083249999999999</v>
+      </c>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
+      <c r="T111" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -16501,7 +18333,7 @@
         <v>19740</v>
       </c>
       <c r="B114" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C114" s="4">
         <v>51</v>
@@ -16531,18 +18363,30 @@
         <v>58</v>
       </c>
       <c r="L114" s="4"/>
-      <c r="M114" s="5"/>
-      <c r="N114" s="6"/>
+      <c r="M114" s="5">
+        <v>4768.3999999999996</v>
+      </c>
+      <c r="N114" s="6">
+        <v>41</v>
+      </c>
       <c r="O114" s="6">
         <v>28</v>
       </c>
-      <c r="P114" s="7"/>
-      <c r="Q114" s="8"/>
-      <c r="R114" s="8"/>
+      <c r="P114" s="7">
+        <v>4.4235780487804881</v>
+      </c>
+      <c r="Q114" s="8">
+        <v>15.307142857142859</v>
+      </c>
+      <c r="R114" s="8">
+        <v>2.9524703703703703</v>
+      </c>
       <c r="S114" s="8">
         <v>8</v>
       </c>
-      <c r="T114" s="9"/>
+      <c r="T114" s="9">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="U114" s="9">
         <v>0.21428571428571427</v>
       </c>
@@ -17524,7 +19368,7 @@
         <v>19752</v>
       </c>
       <c r="B121" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C121" s="4">
         <v>51</v>
@@ -17552,35 +19396,93 @@
         <v>58</v>
       </c>
       <c r="L121" s="4"/>
-      <c r="M121" s="5"/>
-      <c r="N121" s="6"/>
-      <c r="O121" s="6"/>
-      <c r="P121" s="7"/>
-      <c r="Q121" s="8"/>
-      <c r="R121" s="8"/>
-      <c r="S121" s="8"/>
-      <c r="T121" s="9"/>
-      <c r="U121" s="9"/>
-      <c r="V121" s="9"/>
-      <c r="W121" s="9"/>
-      <c r="X121" s="9"/>
-      <c r="Y121" s="9"/>
-      <c r="Z121" s="9"/>
-      <c r="AA121" s="9"/>
-      <c r="AB121" s="9"/>
-      <c r="AC121" s="9"/>
-      <c r="AD121" s="6"/>
-      <c r="AE121" s="6"/>
-      <c r="AF121" s="6"/>
-      <c r="AG121" s="6"/>
-      <c r="AH121" s="6"/>
-      <c r="AI121" s="6"/>
-      <c r="AJ121" s="6"/>
-      <c r="AK121" s="6"/>
-      <c r="AL121" s="6"/>
-      <c r="AM121" s="6"/>
-      <c r="AN121" s="9"/>
-      <c r="AO121" s="6"/>
+      <c r="M121" s="5">
+        <v>2764.1500000000001</v>
+      </c>
+      <c r="N121" s="6">
+        <v>28</v>
+      </c>
+      <c r="O121" s="6">
+        <v>13</v>
+      </c>
+      <c r="P121" s="7">
+        <v>4.9964285714285719</v>
+      </c>
+      <c r="Q121" s="8">
+        <v>16.558976923076923</v>
+      </c>
+      <c r="R121" s="8">
+        <v>4.4359000000000002</v>
+      </c>
+      <c r="S121" s="8">
+        <v>8</v>
+      </c>
+      <c r="T121" s="9">
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="U121" s="9">
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="V121" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="W121" s="9">
+        <v>0</v>
+      </c>
+      <c r="X121" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y121" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z121" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA121" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB121" s="9">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="AC121" s="9">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="AD121" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE121" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF121" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG121" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH121" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI121" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ121" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK121" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL121" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM121" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN121" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO121" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP121" s="4">
         <v>58</v>
       </c>
@@ -18563,7 +20465,7 @@
         <v>19762</v>
       </c>
       <c r="B128" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C128" s="4">
         <v>51</v>
@@ -18593,18 +20495,30 @@
         <v>199</v>
       </c>
       <c r="L128" s="4"/>
-      <c r="M128" s="5"/>
-      <c r="N128" s="6"/>
+      <c r="M128" s="5">
+        <v>2201.3000000000002</v>
+      </c>
+      <c r="N128" s="6">
+        <v>26</v>
+      </c>
       <c r="O128" s="6">
         <v>18</v>
       </c>
-      <c r="P128" s="7"/>
-      <c r="Q128" s="8"/>
-      <c r="R128" s="8"/>
+      <c r="P128" s="7">
+        <v>7.3893320000000005</v>
+      </c>
+      <c r="Q128" s="8">
+        <v>23.837038888888891</v>
+      </c>
+      <c r="R128" s="8">
+        <v>8.2101833333333332</v>
+      </c>
       <c r="S128" s="8">
         <v>7</v>
       </c>
-      <c r="T128" s="9"/>
+      <c r="T128" s="9">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="U128" s="9">
         <v>0.055555555555555552</v>
       </c>
@@ -19022,7 +20936,7 @@
         <v>19772</v>
       </c>
       <c r="B131" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C131" s="4">
         <v>51</v>
@@ -19052,35 +20966,93 @@
         <v>58</v>
       </c>
       <c r="L131" s="4"/>
-      <c r="M131" s="5"/>
-      <c r="N131" s="6"/>
-      <c r="O131" s="6"/>
-      <c r="P131" s="7"/>
-      <c r="Q131" s="8"/>
-      <c r="R131" s="8"/>
-      <c r="S131" s="8"/>
-      <c r="T131" s="9"/>
-      <c r="U131" s="9"/>
-      <c r="V131" s="9"/>
-      <c r="W131" s="9"/>
-      <c r="X131" s="9"/>
-      <c r="Y131" s="9"/>
-      <c r="Z131" s="9"/>
-      <c r="AA131" s="9"/>
-      <c r="AB131" s="9"/>
-      <c r="AC131" s="9"/>
-      <c r="AD131" s="6"/>
-      <c r="AE131" s="6"/>
-      <c r="AF131" s="6"/>
-      <c r="AG131" s="6"/>
-      <c r="AH131" s="6"/>
-      <c r="AI131" s="6"/>
-      <c r="AJ131" s="6"/>
-      <c r="AK131" s="6"/>
-      <c r="AL131" s="6"/>
-      <c r="AM131" s="6"/>
-      <c r="AN131" s="9"/>
-      <c r="AO131" s="6"/>
+      <c r="M131" s="5">
+        <v>2691.5500000000002</v>
+      </c>
+      <c r="N131" s="6">
+        <v>30</v>
+      </c>
+      <c r="O131" s="6">
+        <v>5</v>
+      </c>
+      <c r="P131" s="7">
+        <v>5.7953319999999993</v>
+      </c>
+      <c r="Q131" s="8">
+        <v>24.759999999999998</v>
+      </c>
+      <c r="R131" s="8">
+        <v>12.38334</v>
+      </c>
+      <c r="S131" s="8">
+        <v>7</v>
+      </c>
+      <c r="T131" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="U131" s="9">
+        <v>0</v>
+      </c>
+      <c r="V131" s="9">
+        <v>0</v>
+      </c>
+      <c r="W131" s="9">
+        <v>0</v>
+      </c>
+      <c r="X131" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y131" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z131" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA131" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB131" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC131" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD131" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE131" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF131" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG131" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH131" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI131" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ131" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK131" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL131" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM131" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN131" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO131" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP131" s="4">
         <v>58</v>
       </c>
@@ -19628,7 +21600,9 @@
       <c r="N135" s="6">
         <v>44</v>
       </c>
-      <c r="O135" s="6"/>
+      <c r="O135" s="6">
+        <v>26</v>
+      </c>
       <c r="P135" s="7">
         <v>3.4248069767441858</v>
       </c>
@@ -19638,31 +21612,75 @@
       <c r="R135" s="8">
         <v>2.4788461538461539</v>
       </c>
-      <c r="S135" s="8"/>
+      <c r="S135" s="8">
+        <v>7</v>
+      </c>
       <c r="T135" s="9">
         <v>0.84615384615384615</v>
       </c>
-      <c r="U135" s="9"/>
-      <c r="V135" s="9"/>
-      <c r="W135" s="9"/>
-      <c r="X135" s="9"/>
-      <c r="Y135" s="9"/>
-      <c r="Z135" s="9"/>
-      <c r="AA135" s="9"/>
-      <c r="AB135" s="9"/>
-      <c r="AC135" s="9"/>
-      <c r="AD135" s="6"/>
-      <c r="AE135" s="6"/>
-      <c r="AF135" s="6"/>
-      <c r="AG135" s="6"/>
-      <c r="AH135" s="6"/>
-      <c r="AI135" s="6"/>
-      <c r="AJ135" s="6"/>
-      <c r="AK135" s="6"/>
-      <c r="AL135" s="6"/>
-      <c r="AM135" s="6"/>
-      <c r="AN135" s="9"/>
-      <c r="AO135" s="6"/>
+      <c r="U135" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="V135" s="9">
+        <v>0</v>
+      </c>
+      <c r="W135" s="9">
+        <v>0</v>
+      </c>
+      <c r="X135" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y135" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z135" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA135" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="AB135" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC135" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD135" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE135" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF135" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG135" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH135" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI135" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ135" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK135" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL135" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM135" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN135" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO135" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP135" s="4">
         <v>58</v>
       </c>
@@ -19894,7 +21912,9 @@
       <c r="N137" s="6">
         <v>22</v>
       </c>
-      <c r="O137" s="6"/>
+      <c r="O137" s="6">
+        <v>5</v>
+      </c>
       <c r="P137" s="7">
         <v>5.2219681818181822</v>
       </c>
@@ -19904,31 +21924,75 @@
       <c r="R137" s="8">
         <v>6.4566599999999994</v>
       </c>
-      <c r="S137" s="8"/>
+      <c r="S137" s="8">
+        <v>7</v>
+      </c>
       <c r="T137" s="9">
         <v>0.20000000000000001</v>
       </c>
-      <c r="U137" s="9"/>
-      <c r="V137" s="9"/>
-      <c r="W137" s="9"/>
-      <c r="X137" s="9"/>
-      <c r="Y137" s="9"/>
-      <c r="Z137" s="9"/>
-      <c r="AA137" s="9"/>
-      <c r="AB137" s="9"/>
-      <c r="AC137" s="9"/>
-      <c r="AD137" s="6"/>
-      <c r="AE137" s="6"/>
-      <c r="AF137" s="6"/>
-      <c r="AG137" s="6"/>
-      <c r="AH137" s="6"/>
-      <c r="AI137" s="6"/>
-      <c r="AJ137" s="6"/>
-      <c r="AK137" s="6"/>
-      <c r="AL137" s="6"/>
-      <c r="AM137" s="6"/>
-      <c r="AN137" s="9"/>
-      <c r="AO137" s="6"/>
+      <c r="U137" s="9">
+        <v>0</v>
+      </c>
+      <c r="V137" s="9">
+        <v>0</v>
+      </c>
+      <c r="W137" s="9">
+        <v>0</v>
+      </c>
+      <c r="X137" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y137" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z137" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA137" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB137" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC137" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM137" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN137" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO137" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP137" s="4">
         <v>58</v>
       </c>
@@ -20479,7 +22543,7 @@
         <v>19794</v>
       </c>
       <c r="B142" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C142" s="4">
         <v>51</v>
@@ -20507,35 +22571,93 @@
         <v>58</v>
       </c>
       <c r="L142" s="4"/>
-      <c r="M142" s="5"/>
-      <c r="N142" s="6"/>
-      <c r="O142" s="6"/>
-      <c r="P142" s="7"/>
-      <c r="Q142" s="8"/>
-      <c r="R142" s="8"/>
-      <c r="S142" s="8"/>
-      <c r="T142" s="9"/>
-      <c r="U142" s="9"/>
-      <c r="V142" s="9"/>
-      <c r="W142" s="9"/>
-      <c r="X142" s="9"/>
-      <c r="Y142" s="9"/>
-      <c r="Z142" s="9"/>
-      <c r="AA142" s="9"/>
-      <c r="AB142" s="9"/>
-      <c r="AC142" s="9"/>
-      <c r="AD142" s="6"/>
-      <c r="AE142" s="6"/>
-      <c r="AF142" s="6"/>
-      <c r="AG142" s="6"/>
-      <c r="AH142" s="6"/>
-      <c r="AI142" s="6"/>
-      <c r="AJ142" s="6"/>
-      <c r="AK142" s="6"/>
-      <c r="AL142" s="6"/>
-      <c r="AM142" s="6"/>
-      <c r="AN142" s="9"/>
-      <c r="AO142" s="6"/>
+      <c r="M142" s="5">
+        <v>6233.1999999999998</v>
+      </c>
+      <c r="N142" s="6">
+        <v>60</v>
+      </c>
+      <c r="O142" s="6">
+        <v>36</v>
+      </c>
+      <c r="P142" s="7">
+        <v>3.6155550000000001</v>
+      </c>
+      <c r="Q142" s="8">
+        <v>17.375925000000002</v>
+      </c>
+      <c r="R142" s="8">
+        <v>4.8328694444444444</v>
+      </c>
+      <c r="S142" s="8">
+        <v>8.9000000000000004</v>
+      </c>
+      <c r="T142" s="9">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="U142" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="V142" s="9">
+        <v>0</v>
+      </c>
+      <c r="W142" s="9">
+        <v>0</v>
+      </c>
+      <c r="X142" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y142" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA142" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="AB142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD142" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE142" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK142" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM142" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN142" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO142" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP142" s="4">
         <v>58</v>
       </c>
@@ -20888,7 +23010,7 @@
         <v>19804</v>
       </c>
       <c r="B145" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C145" s="4">
         <v>51</v>
@@ -20918,35 +23040,93 @@
         <v>58</v>
       </c>
       <c r="L145" s="4"/>
-      <c r="M145" s="5"/>
-      <c r="N145" s="6"/>
-      <c r="O145" s="6"/>
-      <c r="P145" s="7"/>
-      <c r="Q145" s="8"/>
-      <c r="R145" s="8"/>
-      <c r="S145" s="8"/>
-      <c r="T145" s="9"/>
-      <c r="U145" s="9"/>
-      <c r="V145" s="9"/>
-      <c r="W145" s="9"/>
-      <c r="X145" s="9"/>
-      <c r="Y145" s="9"/>
-      <c r="Z145" s="9"/>
-      <c r="AA145" s="9"/>
-      <c r="AB145" s="9"/>
-      <c r="AC145" s="9"/>
-      <c r="AD145" s="6"/>
-      <c r="AE145" s="6"/>
-      <c r="AF145" s="6"/>
-      <c r="AG145" s="6"/>
-      <c r="AH145" s="6"/>
-      <c r="AI145" s="6"/>
-      <c r="AJ145" s="6"/>
-      <c r="AK145" s="6"/>
-      <c r="AL145" s="6"/>
-      <c r="AM145" s="6"/>
-      <c r="AN145" s="9"/>
-      <c r="AO145" s="6"/>
+      <c r="M145" s="5">
+        <v>3171.0100000000002</v>
+      </c>
+      <c r="N145" s="6">
+        <v>41</v>
+      </c>
+      <c r="O145" s="6">
+        <v>34</v>
+      </c>
+      <c r="P145" s="7">
+        <v>4.7418707317073165</v>
+      </c>
+      <c r="Q145" s="8">
+        <v>14.576961764705882</v>
+      </c>
+      <c r="R145" s="8">
+        <v>5.5236124999999996</v>
+      </c>
+      <c r="S145" s="8">
+        <v>7</v>
+      </c>
+      <c r="T145" s="9">
+        <v>0.70588235294117652</v>
+      </c>
+      <c r="U145" s="9">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="V145" s="9">
+        <v>0</v>
+      </c>
+      <c r="W145" s="9">
+        <v>0</v>
+      </c>
+      <c r="X145" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="Y145" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="Z145" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AA145" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="AB145" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AC145" s="9">
+        <v>0.41176470588235292</v>
+      </c>
+      <c r="AD145" s="6">
+        <v>38</v>
+      </c>
+      <c r="AE145" s="6">
+        <v>26</v>
+      </c>
+      <c r="AF145" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG145" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH145" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI145" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ145" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK145" s="6">
+        <v>17</v>
+      </c>
+      <c r="AL145" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM145" s="6">
+        <v>14</v>
+      </c>
+      <c r="AN145" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO145" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP145" s="4">
         <v>58</v>
       </c>
@@ -21023,7 +23203,9 @@
       <c r="N146" s="6">
         <v>73</v>
       </c>
-      <c r="O146" s="6"/>
+      <c r="O146" s="6">
+        <v>58</v>
+      </c>
       <c r="P146" s="7">
         <v>3.3013333333333335</v>
       </c>
@@ -21033,31 +23215,75 @@
       <c r="R146" s="8">
         <v>3.87615</v>
       </c>
-      <c r="S146" s="8"/>
+      <c r="S146" s="8">
+        <v>6</v>
+      </c>
       <c r="T146" s="9">
         <v>0.74137931034482762</v>
       </c>
-      <c r="U146" s="9"/>
-      <c r="V146" s="9"/>
-      <c r="W146" s="9"/>
-      <c r="X146" s="9"/>
-      <c r="Y146" s="9"/>
-      <c r="Z146" s="9"/>
-      <c r="AA146" s="9"/>
-      <c r="AB146" s="9"/>
-      <c r="AC146" s="9"/>
-      <c r="AD146" s="6"/>
-      <c r="AE146" s="6"/>
-      <c r="AF146" s="6"/>
-      <c r="AG146" s="6"/>
-      <c r="AH146" s="6"/>
-      <c r="AI146" s="6"/>
-      <c r="AJ146" s="6"/>
-      <c r="AK146" s="6"/>
-      <c r="AL146" s="6"/>
-      <c r="AM146" s="6"/>
-      <c r="AN146" s="9"/>
-      <c r="AO146" s="6"/>
+      <c r="U146" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="V146" s="9">
+        <v>0.017241379310344827</v>
+      </c>
+      <c r="W146" s="9">
+        <v>0</v>
+      </c>
+      <c r="X146" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="Y146" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z146" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA146" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB146" s="9">
+        <v>0.017241379310344827</v>
+      </c>
+      <c r="AC146" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD146" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE146" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF146" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG146" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH146" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI146" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ146" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK146" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL146" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM146" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN146" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO146" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP146" s="4">
         <v>58</v>
       </c>
@@ -21255,7 +23481,7 @@
         <v>19809</v>
       </c>
       <c r="B148" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C148" s="4">
         <v>51</v>
@@ -21285,35 +23511,93 @@
         <v>58</v>
       </c>
       <c r="L148" s="4"/>
-      <c r="M148" s="5"/>
-      <c r="N148" s="6"/>
-      <c r="O148" s="6"/>
-      <c r="P148" s="7"/>
-      <c r="Q148" s="8"/>
-      <c r="R148" s="8"/>
-      <c r="S148" s="8"/>
-      <c r="T148" s="9"/>
-      <c r="U148" s="9"/>
-      <c r="V148" s="9"/>
-      <c r="W148" s="9"/>
-      <c r="X148" s="9"/>
-      <c r="Y148" s="9"/>
-      <c r="Z148" s="9"/>
-      <c r="AA148" s="9"/>
-      <c r="AB148" s="9"/>
-      <c r="AC148" s="9"/>
-      <c r="AD148" s="6"/>
-      <c r="AE148" s="6"/>
-      <c r="AF148" s="6"/>
-      <c r="AG148" s="6"/>
-      <c r="AH148" s="6"/>
-      <c r="AI148" s="6"/>
-      <c r="AJ148" s="6"/>
-      <c r="AK148" s="6"/>
-      <c r="AL148" s="6"/>
-      <c r="AM148" s="6"/>
-      <c r="AN148" s="9"/>
-      <c r="AO148" s="6"/>
+      <c r="M148" s="5">
+        <v>4982.5299999999997</v>
+      </c>
+      <c r="N148" s="6">
+        <v>62</v>
+      </c>
+      <c r="O148" s="6">
+        <v>49</v>
+      </c>
+      <c r="P148" s="7">
+        <v>6.1789062499999998</v>
+      </c>
+      <c r="Q148" s="8">
+        <v>19.017729787234043</v>
+      </c>
+      <c r="R148" s="8">
+        <v>6.8307026315789479</v>
+      </c>
+      <c r="S148" s="8">
+        <v>8</v>
+      </c>
+      <c r="T148" s="9">
+        <v>0.2978723404255319</v>
+      </c>
+      <c r="U148" s="9">
+        <v>0.61224489795918369</v>
+      </c>
+      <c r="V148" s="9">
+        <v>0</v>
+      </c>
+      <c r="W148" s="9">
+        <v>0</v>
+      </c>
+      <c r="X148" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="Y148" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z148" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA148" s="9">
+        <v>0.20408163265306123</v>
+      </c>
+      <c r="AB148" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AC148" s="9">
+        <v>0.22448979591836735</v>
+      </c>
+      <c r="AD148" s="6">
+        <v>36</v>
+      </c>
+      <c r="AE148" s="6">
+        <v>30</v>
+      </c>
+      <c r="AF148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH148" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ148" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK148" s="6">
+        <v>10</v>
+      </c>
+      <c r="AL148" s="6">
+        <v>14</v>
+      </c>
+      <c r="AM148" s="6">
+        <v>11</v>
+      </c>
+      <c r="AN148" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO148" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP148" s="4">
         <v>58</v>
       </c>
@@ -21354,7 +23638,7 @@
         <v>19817</v>
       </c>
       <c r="B149" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C149" s="4">
         <v>51</v>
@@ -21384,18 +23668,30 @@
         <v>58</v>
       </c>
       <c r="L149" s="4"/>
-      <c r="M149" s="5"/>
-      <c r="N149" s="6"/>
+      <c r="M149" s="5">
+        <v>3085.5799999999999</v>
+      </c>
+      <c r="N149" s="6">
+        <v>36</v>
+      </c>
       <c r="O149" s="6">
         <v>21</v>
       </c>
-      <c r="P149" s="7"/>
-      <c r="Q149" s="8"/>
-      <c r="R149" s="8"/>
+      <c r="P149" s="7">
+        <v>6.8680555555555554</v>
+      </c>
+      <c r="Q149" s="8">
+        <v>21.996823809523807</v>
+      </c>
+      <c r="R149" s="8">
+        <v>8.2563476190476184</v>
+      </c>
       <c r="S149" s="8">
         <v>7</v>
       </c>
-      <c r="T149" s="9"/>
+      <c r="T149" s="9">
+        <v>0.19047619047619047</v>
+      </c>
       <c r="U149" s="9">
         <v>0.047619047619047616</v>
       </c>
@@ -21654,7 +23950,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -21684,35 +23980,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>2397.2800000000002</v>
+      </c>
+      <c r="N151" s="6">
+        <v>42</v>
+      </c>
+      <c r="O151" s="6">
+        <v>40</v>
+      </c>
+      <c r="P151" s="7">
+        <v>4.5622222222222222</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>15.2720825</v>
+      </c>
+      <c r="R151" s="8">
+        <v>4.2364026315789474</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0.025000000000000001</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -22067,7 +24421,7 @@
         <v>19843</v>
       </c>
       <c r="B154" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C154" s="4">
         <v>51</v>
@@ -22097,35 +24451,93 @@
         <v>58</v>
       </c>
       <c r="L154" s="4"/>
-      <c r="M154" s="5"/>
-      <c r="N154" s="6"/>
-      <c r="O154" s="6"/>
-      <c r="P154" s="7"/>
-      <c r="Q154" s="8"/>
-      <c r="R154" s="8"/>
-      <c r="S154" s="8"/>
-      <c r="T154" s="9"/>
-      <c r="U154" s="9"/>
-      <c r="V154" s="9"/>
-      <c r="W154" s="9"/>
-      <c r="X154" s="9"/>
-      <c r="Y154" s="9"/>
-      <c r="Z154" s="9"/>
-      <c r="AA154" s="9"/>
-      <c r="AB154" s="9"/>
-      <c r="AC154" s="9"/>
-      <c r="AD154" s="6"/>
-      <c r="AE154" s="6"/>
-      <c r="AF154" s="6"/>
-      <c r="AG154" s="6"/>
-      <c r="AH154" s="6"/>
-      <c r="AI154" s="6"/>
-      <c r="AJ154" s="6"/>
-      <c r="AK154" s="6"/>
-      <c r="AL154" s="6"/>
-      <c r="AM154" s="6"/>
-      <c r="AN154" s="9"/>
-      <c r="AO154" s="6"/>
+      <c r="M154" s="5">
+        <v>2857.7800000000002</v>
+      </c>
+      <c r="N154" s="6">
+        <v>27</v>
+      </c>
+      <c r="O154" s="6">
+        <v>13</v>
+      </c>
+      <c r="P154" s="7">
+        <v>1.2854166666666667</v>
+      </c>
+      <c r="Q154" s="8">
+        <v>10.917946153846154</v>
+      </c>
+      <c r="R154" s="8">
+        <v>1.425</v>
+      </c>
+      <c r="S154" s="8">
+        <v>9</v>
+      </c>
+      <c r="T154" s="9">
+        <v>1</v>
+      </c>
+      <c r="U154" s="9">
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="V154" s="9">
+        <v>0</v>
+      </c>
+      <c r="W154" s="9">
+        <v>0</v>
+      </c>
+      <c r="X154" s="9">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="Y154" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z154" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA154" s="9">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="AB154" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC154" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD154" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE154" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF154" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG154" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH154" s="6">
+        <v>6</v>
+      </c>
+      <c r="AI154" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ154" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK154" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL154" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM154" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN154" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO154" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP154" s="4">
         <v>58</v>
       </c>
@@ -22357,7 +24769,9 @@
       <c r="N156" s="6">
         <v>40</v>
       </c>
-      <c r="O156" s="6"/>
+      <c r="O156" s="6">
+        <v>32</v>
+      </c>
       <c r="P156" s="7">
         <v>6.2815789473684207</v>
       </c>
@@ -22367,31 +24781,75 @@
       <c r="R156" s="8">
         <v>5.8435483870967744</v>
       </c>
-      <c r="S156" s="8"/>
+      <c r="S156" s="8">
+        <v>7</v>
+      </c>
       <c r="T156" s="9">
         <v>0.25</v>
       </c>
-      <c r="U156" s="9"/>
-      <c r="V156" s="9"/>
-      <c r="W156" s="9"/>
-      <c r="X156" s="9"/>
-      <c r="Y156" s="9"/>
-      <c r="Z156" s="9"/>
-      <c r="AA156" s="9"/>
-      <c r="AB156" s="9"/>
-      <c r="AC156" s="9"/>
-      <c r="AD156" s="6"/>
-      <c r="AE156" s="6"/>
-      <c r="AF156" s="6"/>
-      <c r="AG156" s="6"/>
-      <c r="AH156" s="6"/>
-      <c r="AI156" s="6"/>
-      <c r="AJ156" s="6"/>
-      <c r="AK156" s="6"/>
-      <c r="AL156" s="6"/>
-      <c r="AM156" s="6"/>
-      <c r="AN156" s="9"/>
-      <c r="AO156" s="6"/>
+      <c r="U156" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V156" s="9">
+        <v>0</v>
+      </c>
+      <c r="W156" s="9">
+        <v>0</v>
+      </c>
+      <c r="X156" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Y156" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="Z156" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA156" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="AB156" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AC156" s="9">
+        <v>0.1875</v>
+      </c>
+      <c r="AD156" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE156" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF156" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG156" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH156" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI156" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ156" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK156" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL156" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM156" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN156" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO156" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP156" s="4">
         <v>58</v>
       </c>
@@ -22630,7 +25088,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>51</v>
@@ -22660,35 +25118,93 @@
         <v>58</v>
       </c>
       <c r="L159" s="4"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="6"/>
-      <c r="O159" s="6"/>
-      <c r="P159" s="7"/>
-      <c r="Q159" s="8"/>
-      <c r="R159" s="8"/>
-      <c r="S159" s="8"/>
-      <c r="T159" s="9"/>
-      <c r="U159" s="9"/>
-      <c r="V159" s="9"/>
-      <c r="W159" s="9"/>
-      <c r="X159" s="9"/>
-      <c r="Y159" s="9"/>
-      <c r="Z159" s="9"/>
-      <c r="AA159" s="9"/>
-      <c r="AB159" s="9"/>
-      <c r="AC159" s="9"/>
-      <c r="AD159" s="6"/>
-      <c r="AE159" s="6"/>
-      <c r="AF159" s="6"/>
-      <c r="AG159" s="6"/>
-      <c r="AH159" s="6"/>
-      <c r="AI159" s="6"/>
-      <c r="AJ159" s="6"/>
-      <c r="AK159" s="6"/>
-      <c r="AL159" s="6"/>
-      <c r="AM159" s="6"/>
-      <c r="AN159" s="9"/>
-      <c r="AO159" s="6"/>
+      <c r="M159" s="5">
+        <v>7111.5100000000002</v>
+      </c>
+      <c r="N159" s="6">
+        <v>71</v>
+      </c>
+      <c r="O159" s="6">
+        <v>56</v>
+      </c>
+      <c r="P159" s="7">
+        <v>6.1208333333333336</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>19.90267857142857</v>
+      </c>
+      <c r="R159" s="8">
+        <v>6.2744053571428564</v>
+      </c>
+      <c r="S159" s="8">
+        <v>7</v>
+      </c>
+      <c r="T159" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="U159" s="9">
+        <v>0.089285714285714288</v>
+      </c>
+      <c r="V159" s="9">
+        <v>0</v>
+      </c>
+      <c r="W159" s="9">
+        <v>0</v>
+      </c>
+      <c r="X159" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y159" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z159" s="9">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="AA159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB159" s="9">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="AC159" s="9">
+        <v>0.053571428571428568</v>
+      </c>
+      <c r="AD159" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ159" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK159" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL159" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM159" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN159" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO159" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP159" s="4">
         <v>58</v>
       </c>
@@ -22985,7 +25501,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -23015,35 +25531,93 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
-      <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
-      <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="M162" s="5">
+        <v>4216.21</v>
+      </c>
+      <c r="N162" s="6">
+        <v>48</v>
+      </c>
+      <c r="O162" s="6">
+        <v>20</v>
+      </c>
+      <c r="P162" s="7">
+        <v>10.232954545454545</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>21.7225</v>
+      </c>
+      <c r="R162" s="8">
+        <v>5.2481499999999999</v>
+      </c>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
+      <c r="T162" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="U162" s="9">
+        <v>0.34999999999999998</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -23139,7 +25713,7 @@
         <v>0.37333333333333335</v>
       </c>
       <c r="U163" s="9">
-        <v>0.21333333333333335</v>
+        <v>0.22666666666666666</v>
       </c>
       <c r="V163" s="9">
         <v>0</v>
@@ -23166,10 +25740,10 @@
         <v>0</v>
       </c>
       <c r="AD163" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE163" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AF163" s="6">
         <v>0</v>
@@ -23196,10 +25770,10 @@
         <v>0</v>
       </c>
       <c r="AN163" s="9">
-        <v>0</v>
+        <v>0.013333333333333334</v>
       </c>
       <c r="AO163" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="s" r="AP163" s="4">
         <v>58</v>
@@ -24125,7 +26699,7 @@
         <v>19888</v>
       </c>
       <c r="B170" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C170" s="4">
         <v>51</v>
@@ -24155,35 +26729,93 @@
         <v>58</v>
       </c>
       <c r="L170" s="4"/>
-      <c r="M170" s="5"/>
-      <c r="N170" s="6"/>
-      <c r="O170" s="6"/>
-      <c r="P170" s="7"/>
-      <c r="Q170" s="8"/>
-      <c r="R170" s="8"/>
-      <c r="S170" s="8"/>
-      <c r="T170" s="9"/>
-      <c r="U170" s="9"/>
-      <c r="V170" s="9"/>
-      <c r="W170" s="9"/>
-      <c r="X170" s="9"/>
-      <c r="Y170" s="9"/>
-      <c r="Z170" s="9"/>
-      <c r="AA170" s="9"/>
-      <c r="AB170" s="9"/>
-      <c r="AC170" s="9"/>
-      <c r="AD170" s="6"/>
-      <c r="AE170" s="6"/>
-      <c r="AF170" s="6"/>
-      <c r="AG170" s="6"/>
-      <c r="AH170" s="6"/>
-      <c r="AI170" s="6"/>
-      <c r="AJ170" s="6"/>
-      <c r="AK170" s="6"/>
-      <c r="AL170" s="6"/>
-      <c r="AM170" s="6"/>
-      <c r="AN170" s="9"/>
-      <c r="AO170" s="6"/>
+      <c r="M170" s="5">
+        <v>3964.0599999999999</v>
+      </c>
+      <c r="N170" s="6">
+        <v>38</v>
+      </c>
+      <c r="O170" s="6">
+        <v>35</v>
+      </c>
+      <c r="P170" s="7">
+        <v>5.3416657894736845</v>
+      </c>
+      <c r="Q170" s="8">
+        <v>16.060951428571428</v>
+      </c>
+      <c r="R170" s="8">
+        <v>3.7576199999999997</v>
+      </c>
+      <c r="S170" s="8">
+        <v>7</v>
+      </c>
+      <c r="T170" s="9">
+        <v>0.59999999999999998</v>
+      </c>
+      <c r="U170" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="V170" s="9">
+        <v>0</v>
+      </c>
+      <c r="W170" s="9">
+        <v>0</v>
+      </c>
+      <c r="X170" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y170" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z170" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA170" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB170" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC170" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="AD170" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE170" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF170" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG170" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH170" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI170" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ170" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK170" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL170" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM170" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN170" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO170" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP170" s="4">
         <v>58</v>
       </c>
@@ -24850,7 +27482,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>51</v>
@@ -24880,35 +27512,93 @@
         <v>58</v>
       </c>
       <c r="L175" s="4"/>
-      <c r="M175" s="5"/>
-      <c r="N175" s="6"/>
-      <c r="O175" s="6"/>
-      <c r="P175" s="7"/>
-      <c r="Q175" s="8"/>
-      <c r="R175" s="8"/>
-      <c r="S175" s="8"/>
-      <c r="T175" s="9"/>
-      <c r="U175" s="9"/>
-      <c r="V175" s="9"/>
-      <c r="W175" s="9"/>
-      <c r="X175" s="9"/>
-      <c r="Y175" s="9"/>
-      <c r="Z175" s="9"/>
-      <c r="AA175" s="9"/>
-      <c r="AB175" s="9"/>
-      <c r="AC175" s="9"/>
-      <c r="AD175" s="6"/>
-      <c r="AE175" s="6"/>
-      <c r="AF175" s="6"/>
-      <c r="AG175" s="6"/>
-      <c r="AH175" s="6"/>
-      <c r="AI175" s="6"/>
-      <c r="AJ175" s="6"/>
-      <c r="AK175" s="6"/>
-      <c r="AL175" s="6"/>
-      <c r="AM175" s="6"/>
-      <c r="AN175" s="9"/>
-      <c r="AO175" s="6"/>
+      <c r="M175" s="5">
+        <v>2090.8000000000002</v>
+      </c>
+      <c r="N175" s="6">
+        <v>39</v>
+      </c>
+      <c r="O175" s="6">
+        <v>11</v>
+      </c>
+      <c r="P175" s="7">
+        <v>10.411459375</v>
+      </c>
+      <c r="Q175" s="8">
+        <v>22.325754545454547</v>
+      </c>
+      <c r="R175" s="8">
+        <v>2.2742454545454547</v>
+      </c>
+      <c r="S175" s="8">
+        <v>7</v>
+      </c>
+      <c r="T175" s="9">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="U175" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="V175" s="9">
+        <v>0</v>
+      </c>
+      <c r="W175" s="9">
+        <v>0</v>
+      </c>
+      <c r="X175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA175" s="9">
+        <v>0.090909090909090912</v>
+      </c>
+      <c r="AB175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK175" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM175" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN175" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO175" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP175" s="4">
         <v>58</v>
       </c>
@@ -25140,7 +27830,9 @@
       <c r="N177" s="6">
         <v>31</v>
       </c>
-      <c r="O177" s="6"/>
+      <c r="O177" s="6">
+        <v>17</v>
+      </c>
       <c r="P177" s="7">
         <v>3.1204290322580643</v>
       </c>
@@ -25150,31 +27842,75 @@
       <c r="R177" s="8">
         <v>1.6941176470588235</v>
       </c>
-      <c r="S177" s="8"/>
+      <c r="S177" s="8">
+        <v>7</v>
+      </c>
       <c r="T177" s="9">
         <v>0.94117647058823528</v>
       </c>
-      <c r="U177" s="9"/>
-      <c r="V177" s="9"/>
-      <c r="W177" s="9"/>
-      <c r="X177" s="9"/>
-      <c r="Y177" s="9"/>
-      <c r="Z177" s="9"/>
-      <c r="AA177" s="9"/>
-      <c r="AB177" s="9"/>
-      <c r="AC177" s="9"/>
-      <c r="AD177" s="6"/>
-      <c r="AE177" s="6"/>
-      <c r="AF177" s="6"/>
-      <c r="AG177" s="6"/>
-      <c r="AH177" s="6"/>
-      <c r="AI177" s="6"/>
-      <c r="AJ177" s="6"/>
-      <c r="AK177" s="6"/>
-      <c r="AL177" s="6"/>
-      <c r="AM177" s="6"/>
-      <c r="AN177" s="9"/>
-      <c r="AO177" s="6"/>
+      <c r="U177" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="V177" s="9">
+        <v>0</v>
+      </c>
+      <c r="W177" s="9">
+        <v>0</v>
+      </c>
+      <c r="X177" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="Y177" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z177" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA177" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB177" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC177" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD177" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE177" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF177" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG177" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH177" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI177" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ177" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK177" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL177" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM177" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN177" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO177" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP177" s="4">
         <v>58</v>
       </c>
@@ -25406,7 +28142,9 @@
       <c r="N179" s="6">
         <v>59</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>24</v>
+      </c>
       <c r="P179" s="7">
         <v>6.7635051724137929</v>
       </c>
@@ -25416,31 +28154,75 @@
       <c r="R179" s="8">
         <v>17.006249999999998</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.33333333333333331</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
@@ -25479,7 +28261,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>51</v>
@@ -25509,35 +28291,93 @@
         <v>58</v>
       </c>
       <c r="L180" s="4"/>
-      <c r="M180" s="5"/>
-      <c r="N180" s="6"/>
-      <c r="O180" s="6"/>
-      <c r="P180" s="7"/>
-      <c r="Q180" s="8"/>
-      <c r="R180" s="8"/>
-      <c r="S180" s="8"/>
-      <c r="T180" s="9"/>
-      <c r="U180" s="9"/>
-      <c r="V180" s="9"/>
-      <c r="W180" s="9"/>
-      <c r="X180" s="9"/>
-      <c r="Y180" s="9"/>
-      <c r="Z180" s="9"/>
-      <c r="AA180" s="9"/>
-      <c r="AB180" s="9"/>
-      <c r="AC180" s="9"/>
-      <c r="AD180" s="6"/>
-      <c r="AE180" s="6"/>
-      <c r="AF180" s="6"/>
-      <c r="AG180" s="6"/>
-      <c r="AH180" s="6"/>
-      <c r="AI180" s="6"/>
-      <c r="AJ180" s="6"/>
-      <c r="AK180" s="6"/>
-      <c r="AL180" s="6"/>
-      <c r="AM180" s="6"/>
-      <c r="AN180" s="9"/>
-      <c r="AO180" s="6"/>
+      <c r="M180" s="5">
+        <v>1635.6500000000001</v>
+      </c>
+      <c r="N180" s="6">
+        <v>22</v>
+      </c>
+      <c r="O180" s="6">
+        <v>9</v>
+      </c>
+      <c r="P180" s="7">
+        <v>5.3999999999999995</v>
+      </c>
+      <c r="Q180" s="8">
+        <v>28.544444444444441</v>
+      </c>
+      <c r="R180" s="8">
+        <v>15.135188888888889</v>
+      </c>
+      <c r="S180" s="8">
+        <v>8</v>
+      </c>
+      <c r="T180" s="9">
+        <v>0</v>
+      </c>
+      <c r="U180" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="V180" s="9">
+        <v>0</v>
+      </c>
+      <c r="W180" s="9">
+        <v>0</v>
+      </c>
+      <c r="X180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC180" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AD180" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM180" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO180" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP180" s="4">
         <v>58</v>
       </c>
@@ -26305,7 +29145,7 @@
         <v>19926</v>
       </c>
       <c r="B186" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C186" s="4">
         <v>51</v>
@@ -26335,35 +29175,93 @@
         <v>58</v>
       </c>
       <c r="L186" s="4"/>
-      <c r="M186" s="5"/>
-      <c r="N186" s="6"/>
-      <c r="O186" s="6"/>
-      <c r="P186" s="7"/>
-      <c r="Q186" s="8"/>
-      <c r="R186" s="8"/>
-      <c r="S186" s="8"/>
-      <c r="T186" s="9"/>
-      <c r="U186" s="9"/>
-      <c r="V186" s="9"/>
-      <c r="W186" s="9"/>
-      <c r="X186" s="9"/>
-      <c r="Y186" s="9"/>
-      <c r="Z186" s="9"/>
-      <c r="AA186" s="9"/>
-      <c r="AB186" s="9"/>
-      <c r="AC186" s="9"/>
-      <c r="AD186" s="6"/>
-      <c r="AE186" s="6"/>
-      <c r="AF186" s="6"/>
-      <c r="AG186" s="6"/>
-      <c r="AH186" s="6"/>
-      <c r="AI186" s="6"/>
-      <c r="AJ186" s="6"/>
-      <c r="AK186" s="6"/>
-      <c r="AL186" s="6"/>
-      <c r="AM186" s="6"/>
-      <c r="AN186" s="9"/>
-      <c r="AO186" s="6"/>
+      <c r="M186" s="5">
+        <v>1774.5</v>
+      </c>
+      <c r="N186" s="6">
+        <v>19</v>
+      </c>
+      <c r="O186" s="6">
+        <v>9</v>
+      </c>
+      <c r="P186" s="7">
+        <v>10.379826315789474</v>
+      </c>
+      <c r="Q186" s="8">
+        <v>22.918522222222222</v>
+      </c>
+      <c r="R186" s="8">
+        <v>5.9722222222222223</v>
+      </c>
+      <c r="S186" s="8">
+        <v>7</v>
+      </c>
+      <c r="T186" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="U186" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="V186" s="9">
+        <v>0</v>
+      </c>
+      <c r="W186" s="9">
+        <v>0</v>
+      </c>
+      <c r="X186" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="Y186" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC186" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AD186" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE186" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH186" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL186" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM186" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN186" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO186" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP186" s="4">
         <v>58</v>
       </c>
@@ -26404,7 +29302,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -26434,35 +29332,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>1299.1199999999999</v>
+      </c>
+      <c r="N187" s="6">
+        <v>18</v>
+      </c>
+      <c r="O187" s="6">
+        <v>15</v>
+      </c>
+      <c r="P187" s="7">
+        <v>9.1518500000000014</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>30.658886666666668</v>
+      </c>
+      <c r="R187" s="8">
+        <v>14.85778</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -26660,7 +29616,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -26690,35 +29646,93 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="M189" s="5">
+        <v>5125.0200000000004</v>
+      </c>
+      <c r="N189" s="6">
+        <v>91</v>
+      </c>
+      <c r="O189" s="6">
+        <v>81</v>
+      </c>
+      <c r="P189" s="7">
+        <v>5.740502150537635</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>25.424074074074074</v>
+      </c>
+      <c r="R189" s="8">
+        <v>14.130701315789473</v>
+      </c>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
+      <c r="T189" s="9">
+        <v>0.19753086419753085</v>
+      </c>
+      <c r="U189" s="9">
+        <v>0.59259259259259256</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0.012345679012345678</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.012345679012345678</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0.012345679012345678</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.50617283950617287</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>50</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>48</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>41</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -26759,7 +29773,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -26789,35 +29803,93 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-      <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="M190" s="5">
+        <v>3208.27</v>
+      </c>
+      <c r="N190" s="6">
+        <v>33</v>
+      </c>
+      <c r="O190" s="6">
+        <v>15</v>
+      </c>
+      <c r="P190" s="7">
+        <v>4.663636363636364</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>15.475553333333332</v>
+      </c>
+      <c r="R190" s="8">
+        <v>4.4500000000000002</v>
+      </c>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
+      <c r="T190" s="9">
+        <v>0.73333333333333328</v>
+      </c>
+      <c r="U190" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -27327,7 +30399,7 @@
         <v>19943</v>
       </c>
       <c r="B194" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C194" s="4">
         <v>51</v>
@@ -27357,35 +30429,93 @@
         <v>58</v>
       </c>
       <c r="L194" s="4"/>
-      <c r="M194" s="5"/>
-      <c r="N194" s="6"/>
-      <c r="O194" s="6"/>
-      <c r="P194" s="7"/>
-      <c r="Q194" s="8"/>
-      <c r="R194" s="8"/>
-      <c r="S194" s="8"/>
-      <c r="T194" s="9"/>
-      <c r="U194" s="9"/>
-      <c r="V194" s="9"/>
-      <c r="W194" s="9"/>
-      <c r="X194" s="9"/>
-      <c r="Y194" s="9"/>
-      <c r="Z194" s="9"/>
-      <c r="AA194" s="9"/>
-      <c r="AB194" s="9"/>
-      <c r="AC194" s="9"/>
-      <c r="AD194" s="6"/>
-      <c r="AE194" s="6"/>
-      <c r="AF194" s="6"/>
-      <c r="AG194" s="6"/>
-      <c r="AH194" s="6"/>
-      <c r="AI194" s="6"/>
-      <c r="AJ194" s="6"/>
-      <c r="AK194" s="6"/>
-      <c r="AL194" s="6"/>
-      <c r="AM194" s="6"/>
-      <c r="AN194" s="9"/>
-      <c r="AO194" s="6"/>
+      <c r="M194" s="5">
+        <v>1603.2</v>
+      </c>
+      <c r="N194" s="6">
+        <v>21</v>
+      </c>
+      <c r="O194" s="6">
+        <v>13</v>
+      </c>
+      <c r="P194" s="7">
+        <v>7.1015136363636371</v>
+      </c>
+      <c r="Q194" s="8">
+        <v>20.661538461538463</v>
+      </c>
+      <c r="R194" s="8">
+        <v>6.5972250000000008</v>
+      </c>
+      <c r="S194" s="8">
+        <v>7</v>
+      </c>
+      <c r="T194" s="9">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="U194" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="V194" s="9">
+        <v>0</v>
+      </c>
+      <c r="W194" s="9">
+        <v>0</v>
+      </c>
+      <c r="X194" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="Y194" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA194" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="AB194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD194" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE194" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH194" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK194" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM194" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN194" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO194" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP194" s="4">
         <v>58</v>
       </c>
@@ -27426,7 +30556,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -27456,14 +30586,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>3928.1900000000001</v>
+      </c>
+      <c r="N195" s="6">
+        <v>49</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>4.9840270833333333</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>23.573736363636364</v>
+      </c>
+      <c r="R195" s="8">
+        <v>11.046969696969697</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.15151515151515152</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>
@@ -28153,7 +31295,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>51</v>
@@ -28183,35 +31325,93 @@
         <v>58</v>
       </c>
       <c r="L200" s="4"/>
-      <c r="M200" s="5"/>
-      <c r="N200" s="6"/>
-      <c r="O200" s="6"/>
-      <c r="P200" s="7"/>
-      <c r="Q200" s="8"/>
-      <c r="R200" s="8"/>
-      <c r="S200" s="8"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
-      <c r="W200" s="9"/>
-      <c r="X200" s="9"/>
-      <c r="Y200" s="9"/>
-      <c r="Z200" s="9"/>
-      <c r="AA200" s="9"/>
-      <c r="AB200" s="9"/>
-      <c r="AC200" s="9"/>
-      <c r="AD200" s="6"/>
-      <c r="AE200" s="6"/>
-      <c r="AF200" s="6"/>
-      <c r="AG200" s="6"/>
-      <c r="AH200" s="6"/>
-      <c r="AI200" s="6"/>
-      <c r="AJ200" s="6"/>
-      <c r="AK200" s="6"/>
-      <c r="AL200" s="6"/>
-      <c r="AM200" s="6"/>
-      <c r="AN200" s="9"/>
-      <c r="AO200" s="6"/>
+      <c r="M200" s="5">
+        <v>1433.5899999999999</v>
+      </c>
+      <c r="N200" s="6">
+        <v>17</v>
+      </c>
+      <c r="O200" s="6">
+        <v>11</v>
+      </c>
+      <c r="P200" s="7">
+        <v>10.299017647058823</v>
+      </c>
+      <c r="Q200" s="8">
+        <v>25.722727272727273</v>
+      </c>
+      <c r="R200" s="8">
+        <v>9.0499999999999989</v>
+      </c>
+      <c r="S200" s="8">
+        <v>7</v>
+      </c>
+      <c r="T200" s="9">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="U200" s="9">
+        <v>0</v>
+      </c>
+      <c r="V200" s="9">
+        <v>0</v>
+      </c>
+      <c r="W200" s="9">
+        <v>0</v>
+      </c>
+      <c r="X200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y200" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM200" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN200" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO200" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP200" s="4">
         <v>58</v>
       </c>
@@ -28643,7 +31843,9 @@
       <c r="N204" s="6">
         <v>31</v>
       </c>
-      <c r="O204" s="6"/>
+      <c r="O204" s="6">
+        <v>14</v>
+      </c>
       <c r="P204" s="7">
         <v>6.2465517241379311</v>
       </c>
@@ -28653,31 +31855,75 @@
       <c r="R204" s="8">
         <v>5.2717923076923077</v>
       </c>
-      <c r="S204" s="8"/>
+      <c r="S204" s="8">
+        <v>7</v>
+      </c>
       <c r="T204" s="9">
         <v>0.071428571428571425</v>
       </c>
-      <c r="U204" s="9"/>
-      <c r="V204" s="9"/>
-      <c r="W204" s="9"/>
-      <c r="X204" s="9"/>
-      <c r="Y204" s="9"/>
-      <c r="Z204" s="9"/>
-      <c r="AA204" s="9"/>
-      <c r="AB204" s="9"/>
-      <c r="AC204" s="9"/>
-      <c r="AD204" s="6"/>
-      <c r="AE204" s="6"/>
-      <c r="AF204" s="6"/>
-      <c r="AG204" s="6"/>
-      <c r="AH204" s="6"/>
-      <c r="AI204" s="6"/>
-      <c r="AJ204" s="6"/>
-      <c r="AK204" s="6"/>
-      <c r="AL204" s="6"/>
-      <c r="AM204" s="6"/>
-      <c r="AN204" s="9"/>
-      <c r="AO204" s="6"/>
+      <c r="U204" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="V204" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="W204" s="9">
+        <v>0</v>
+      </c>
+      <c r="X204" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="Y204" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="Z204" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA204" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AB204" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC204" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD204" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE204" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF204" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG204" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH204" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI204" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ204" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK204" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL204" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM204" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN204" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO204" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP204" s="4">
         <v>58</v>
       </c>
@@ -28875,7 +32121,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>51</v>
@@ -28905,35 +32151,93 @@
         <v>58</v>
       </c>
       <c r="L206" s="4"/>
-      <c r="M206" s="5"/>
-      <c r="N206" s="6"/>
-      <c r="O206" s="6"/>
-      <c r="P206" s="7"/>
-      <c r="Q206" s="8"/>
-      <c r="R206" s="8"/>
-      <c r="S206" s="8"/>
-      <c r="T206" s="9"/>
-      <c r="U206" s="9"/>
-      <c r="V206" s="9"/>
-      <c r="W206" s="9"/>
-      <c r="X206" s="9"/>
-      <c r="Y206" s="9"/>
-      <c r="Z206" s="9"/>
-      <c r="AA206" s="9"/>
-      <c r="AB206" s="9"/>
-      <c r="AC206" s="9"/>
-      <c r="AD206" s="6"/>
-      <c r="AE206" s="6"/>
-      <c r="AF206" s="6"/>
-      <c r="AG206" s="6"/>
-      <c r="AH206" s="6"/>
-      <c r="AI206" s="6"/>
-      <c r="AJ206" s="6"/>
-      <c r="AK206" s="6"/>
-      <c r="AL206" s="6"/>
-      <c r="AM206" s="6"/>
-      <c r="AN206" s="9"/>
-      <c r="AO206" s="6"/>
+      <c r="M206" s="5">
+        <v>2598.5999999999999</v>
+      </c>
+      <c r="N206" s="6">
+        <v>28</v>
+      </c>
+      <c r="O206" s="6">
+        <v>16</v>
+      </c>
+      <c r="P206" s="7">
+        <v>6.2404750000000009</v>
+      </c>
+      <c r="Q206" s="8">
+        <v>29.335418749999999</v>
+      </c>
+      <c r="R206" s="8">
+        <v>15.88125</v>
+      </c>
+      <c r="S206" s="8">
+        <v>7</v>
+      </c>
+      <c r="T206" s="9">
+        <v>0</v>
+      </c>
+      <c r="U206" s="9">
+        <v>0</v>
+      </c>
+      <c r="V206" s="9">
+        <v>0</v>
+      </c>
+      <c r="W206" s="9">
+        <v>0</v>
+      </c>
+      <c r="X206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO206" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP206" s="4">
         <v>58</v>
       </c>
